--- a/data/NEISS_Supplement_500_Samples.xlsx
+++ b/data/NEISS_Supplement_500_Samples.xlsx
@@ -660,7 +660,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Mentions 'VERAPMIL' which is an OTC medication, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Mentions 'drug ingestion' which does not specify a supplement or vitamin, so defaulting to label=0.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Mentions 'amphetamines' and 'benzodiazepans', which are medications, not supplements.</t>
+          <t>Mentions 'AMPHETAMINES AND BENZODIAZEPANS', which are drugs/medications, excluded.</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>No mention of vitamins or dietary supplements.</t>
+          <t>Narrative describes scorpion bite and envenomation, with no mention of vitamin ingestion.</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Mentions 'bleach laundry detergent' which is a chemical, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Mentions 'AMMOXIL' which is a medication (antibiotic), not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements, and the substance inhaled is a vape (not a supplement).</t>
+          <t>Narrative describes vaping exposure, not vitamin ingestion.</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Mentions 'paint' which is a household chemical, not a supplement.</t>
+          <t>Narrative describes paint ingestion/exposure, which is a household chemical/toxin, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>No explicit mention of vitamin or supplement, and 'iron' is not mentioned.</t>
+          <t>Narrative describes an unknown 'white substance' and does not mention any specific, safe vitamin or fish oil.</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>No explicit mention of a vitamin or supplement, and mentions 'charcoal activated' which is not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Mentions 'carpet cleaner' which is a household chemical, not a supplement.</t>
+          <t>Ingestion of household chemical ('carpet cleaner'/'detergent') is not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Mentions 'toxicity' which implies ingestion of a non-supplement substance</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Mentions 'Diltiazam tablet' which is a prescription medication, not a supplement.</t>
+          <t>Mentions 'DILTIAZAM TABLET', which is a prescription medication, excluded.</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements, only glucose and insulin.</t>
+          <t>Narrative discusses blood sugar/insulin management and hypoglycemia, not ingestion of a vitamin.</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Eye drops are a medication, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Medication 'aamloidpine/donepezil' and 'grandmother's medicine' are not supplements, they are prescription medications.</t>
+          <t>Mentions 'AMLODIPINE/DONEPEZIL' and 'MEDICATION', which are drugs/medications and are excluded.</t>
         </is>
       </c>
     </row>
@@ -2420,7 +2420,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Mentions 'new medication' which is likely prescription and not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Hydrogen peroxide is a household chemical/toxin, not a supplement.</t>
+          <t>Mentions 'Hydrogen Peroxide', which is a household chemical/toxin, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2644,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>Mentions 'anitihistamine' and 'triprolidine hcl', which are medications, not supplements.</t>
+          <t>Mentions 'antihistamine (15ml) triprolidine hcl', which is a medication, excluded.</t>
         </is>
       </c>
     </row>
@@ -2762,7 +2762,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>Mentions 'bupropion' which is a prescription medication, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>Mentions 'multivitamin' which could be with or without iron; however, no mention of 'no iron' or exclusion of iron-containing formulations.</t>
+          <t>Mentions 'multivitamin' without specifying 'no iron', and general multivitamins are excluded if iron status is unknown or if the formulation is not explicitly confirmed as iron-free.</t>
         </is>
       </c>
     </row>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>Migraine medication is a prescription medication, not a supplement.</t>
+          <t>Mentions 'migraine medication', which is a drug and excluded.</t>
         </is>
       </c>
     </row>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Ingestion alone does NOT imply label=1; no explicit mention of vitamin/supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -3210,7 +3210,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Mentions '*** ODT 8 MG TABLETS' which is a medication (OTC or Rx), not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>RUBBING ALCOHOL is a household chemical, not a supplement.</t>
+          <t>Mentions 'rubbing alcohol' which is a household chemical/toxin, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -3422,7 +3422,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Mentions 'oldersisters meds' which implies prescription medication, not a supplement.</t>
+          <t>Mentions 'MEDS' which is too general and could be any drug/medication, triggering exclusion rules.</t>
         </is>
       </c>
     </row>
@@ -3528,7 +3528,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Methylphenidate is a prescription medication, not a supplement.</t>
+          <t>Mentions 'methylphendate pill', which is a medication, excluded.</t>
         </is>
       </c>
     </row>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Mentions 'scented oil' which is a household chemical, not a supplement.</t>
+          <t>Mentions 'apple cinnamon scented oil', which is a household/scented oil, not a vitamin or fish oil.</t>
         </is>
       </c>
     </row>
@@ -3752,7 +3752,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Mentions 'dogs medication' (prescription medication) and does not mention any vitamin or supplement.</t>
+          <t>Mentions 'TRAMADOL', which is a medication, excluded.</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>Hand sanitizer is a household chemical/toxin, not a supplement.</t>
+          <t>Mentions 'hand sanitizer', which is a household chemical/toxin, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3964,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>Colchicine is an OTC medication for gout treatment, not a vitamin/supplement.</t>
+          <t>Mentions 'COLCHICINE' which is a medication, excluded.</t>
         </is>
       </c>
     </row>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Cough medicine is medication, not a supplement.</t>
+          <t>Mentions 'cough medicine', which is a medication and excluded.</t>
         </is>
       </c>
     </row>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Mentions 'DIET PILL' which implies medication rather than a supplement</t>
+          <t>Hard Rule: Mentions weight-loss/diet supplement.</t>
         </is>
       </c>
     </row>
@@ -4282,7 +4282,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Mentions 'gun oil' which is a household chemical, not a supplement.</t>
+          <t>Mentions 'GUN OIL', which is a household chemical/toxin, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>Mentions 'medicated powder' which is not a clear supplement/vitamin; also mentions household chemical/unknown substance.</t>
+          <t>Mentions 'medicated powder " * * " unknown amount', which is redacted/ambiguous and not a clear vitamin.</t>
         </is>
       </c>
     </row>
@@ -4498,7 +4498,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>No mention of vitamin or dietary supplement; ingestion is accidental but substance not specified.</t>
+          <t>The narrative mentions 'NAME OF DRUG' and is unspecified, which falls under ambiguous/unknown ingestion.</t>
         </is>
       </c>
     </row>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>Mentions 'pills' without specifying supplement or medication, so defaulting to label=0.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Mentions 'laundry detergent' which is a chemical, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -4840,7 +4840,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>Cough &amp; Cold Rx and Allergy Dx are medications, not supplements.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -4946,7 +4946,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>No explicit mention of a vitamin or supplement, and the substance is unknown.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements, and 'candies' is not a specific supplement.</t>
+          <t>Mentions 'lisinopril-hctz', which is a prescription medication, excluded.</t>
         </is>
       </c>
     </row>
@@ -5182,7 +5182,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>No explicit mention of vitamin or dietary supplement, and symptoms started after taking a supplement.</t>
+          <t>Narrative mentions only general 'supplement' without specifying a pure vitamin or fish oil, and does not meet the criteria for label=1.</t>
         </is>
       </c>
     </row>
@@ -5288,7 +5288,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>Mentions 'ADHD medication' and 'dystonic reaction', which are not related to vitamin or dietary supplement ingestion.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -5414,7 +5414,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>Mentions 'hygenic toilet cleaner' which is a household chemical, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>No explicit mention of a vitamin or supplement, and presence of 'laundry detergent' which is a chemical.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -5626,7 +5626,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements; propane gas is a household chemical.</t>
+          <t>Narrative describes inhalation of propane gas, which is a household chemical/toxin, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>Bleach is a household chemical, not a supplement.</t>
+          <t>Involves household chemical 'bleach' exposure, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>Mentions 'cleaning product' which is a household chemical, not a supplement.</t>
+          <t>Narrative describes exposure to a cleaning product, not a vitamin or vitamin supplement.</t>
         </is>
       </c>
     </row>
@@ -5944,7 +5944,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>Mentions 'dissolvable strip' which is a medication delivery system, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements; mentions medication (Warfarin) and household chemical (hot tub)</t>
+          <t>Narrative mentions 'Warfarin', which is a prescription medication, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -6156,7 +6156,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>Unknown substance mentioned, does not clearly indicate a vitamin or dietary supplement.</t>
+          <t>Ingestion of 'cleaning product' is a household chemical/toxin, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>Mentions 'soap' which is a household chemical, not a supplement.</t>
+          <t>Ingestion of 'soap' is a household chemical/toxin, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -6380,7 +6380,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>Mentions 'medicine cup' and 'dosage error', indicating prescription medication was involved.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>No explicit mention of vitamin or supplement, and 'meds' is a general term for medication.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -6612,7 +6612,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>No mention of vitamins or dietary supplements.</t>
+          <t>Narrative discusses cocaine abuse and alcohol intoxication, with no mention of a vitamin or fish oil.</t>
         </is>
       </c>
     </row>
@@ -6718,7 +6718,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>Boric acid is a household chemical/toxin, not a vitamin/supplement.</t>
+          <t>Mentions 'boric acid' which is a household chemical/toxin, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>No explicit mention of a vitamin or supplement; 'possible ingestion' is too vague.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements, only household chemical 'baby oil'.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -7036,7 +7036,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements, and no indication of iron-containing formulation.</t>
+          <t>Narrative describes alcohol use and syncope, with no mention of a vitamin or fish oil.</t>
         </is>
       </c>
     </row>
@@ -7146,7 +7146,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>Lighter fluid is a household chemical, not a supplement.</t>
+          <t>The narrative describes 'lighter fluid' ingestion, which is a household chemical/toxin, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -7256,7 +7256,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>Mentions 'Amlodipine and Triamterene' which are prescription medications, not supplements.</t>
+          <t>Mentions 'amlodipine and triamterene', which are medications, excluded.</t>
         </is>
       </c>
     </row>
@@ -7374,7 +7374,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>Mentions 'hydroxyzine' which is an OTC medication, not a supplement.</t>
+          <t>Mentions 'HYDROXYZINE', which is a medication, excluded.</t>
         </is>
       </c>
     </row>
@@ -7480,7 +7480,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>Guafacine is a prescription medication, not a supplement.</t>
+          <t>Mentions 'GUAFACINE', which is a medication, excluded.</t>
         </is>
       </c>
     </row>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>No mention of vitamin or dietary supplement ingestion/adverse reaction</t>
+          <t>Narrative describes a vaccination reaction, not an ingestion of a vitamin.</t>
         </is>
       </c>
     </row>
@@ -7692,7 +7692,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements.</t>
+          <t>Narrative describes alcohol intoxication and syncope, with no mention of a strictly harmless vitamin or fish oil.</t>
         </is>
       </c>
     </row>
@@ -7798,7 +7798,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>Mentions 'cleaner' which is a household chemical, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -7912,11 +7912,11 @@
         <v>1</v>
       </c>
       <c r="AA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>Mentions 'chewable melatonin tablets' (supplement; no iron mentioned).</t>
+          <t>Hard Rule: Mentions melatonin (non-vitamin supplement).</t>
         </is>
       </c>
     </row>
@@ -8022,7 +8022,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>Bleach is a household chemical, not a supplement.</t>
+          <t>Ingestion of household chemical 'bleach' is not a vitamin and is excluded.</t>
         </is>
       </c>
     </row>
@@ -8128,7 +8128,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>Bleach is a household chemical, not a supplement.</t>
+          <t>Mentions 'BLEACH', household chemicals/toxins are excluded.</t>
         </is>
       </c>
     </row>
@@ -8238,7 +8238,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>Mentions 'iron' in the context of a medication (4 MG TABS) which is excluded.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -8352,11 +8352,11 @@
         <v>1</v>
       </c>
       <c r="AA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>Mentions 'melatonin' (supplement; no iron) and 'gummies' which are a common supplement formulation.</t>
+          <t>Hard Rule: Mentions melatonin (non-vitamin supplement).</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>Ingestion alone does NOT imply label=1; '***' indicates unknown substance.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -8572,7 +8572,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>Ingestion of unknown substance (***), does not explicitly mention vitamin or dietary supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>Mentions '*** pills' which does not specify a vitamin/supplement, and no iron is mentioned.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -8796,7 +8796,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>No explicit mention of a vitamin or supplement, and 'iron' is not mentioned.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -8902,7 +8902,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>No explicit mention of vitamin or dietary supplement; overdose could be from any medication.</t>
+          <t>Narrative is too vague and does not specify a known vitamin or fish oil, and does not mention any excluded substances.</t>
         </is>
       </c>
     </row>
@@ -9008,7 +9008,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>No mention of vitamin or dietary supplement</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements, and the substance 'ETOH' is a medication (alcohol) rather than a supplement.</t>
+          <t>Narrative describes ingestion of 'bleachersat school' and 'ETOH', which are not specified as a pure vitamin or fish oil, and 'bleachersat school' is ambiguous.</t>
         </is>
       </c>
     </row>
@@ -9220,7 +9220,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>Ingestion alone does NOT imply label=1; no explicit mention of vitamin/supplement</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -9326,7 +9326,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements; narrative mentions immunization shot and fever/irritability.</t>
+          <t>The narrative describes an immunization shot and symptoms, with no mention of vitamin ingestion.</t>
         </is>
       </c>
     </row>
@@ -9432,7 +9432,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements.</t>
+          <t>Narrative describes alcohol ingestion and fall, no mention of vitamins or specified safe supplements.</t>
         </is>
       </c>
     </row>
@@ -9550,7 +9550,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>Nail polish is a household chemical/toxin, not a supplement.</t>
+          <t>Ingestion of nail polish is a household chemical/toxin, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -9656,7 +9656,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>Ingestion alone does NOT imply label=1; no explicit mention of vitamin/supplement</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>Unknown substance ingested, does not explicitly mention a vitamin or supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -9880,7 +9880,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>No explicit mention of vitamin or dietary supplement; ingestion alone does not imply label=1</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -9986,7 +9986,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements, and the narrative is focused on medication (warfarin) and medical condition (intercranial hemorrhage).</t>
+          <t>Narrative mentions 'WARFARIN', which is a medication, and does not involve a vitamin ingestion.</t>
         </is>
       </c>
     </row>
@@ -10092,7 +10092,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements; compressed air cans are not a supplement.</t>
+          <t>Ingesting compressed air cans is a household chemical/toxin, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -10202,7 +10202,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>Aspirin is an OTC medication, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>No explicit mention of vitamin or dietary supplement; 'PM' is unclear and does not imply a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>Sertraline is an OTC medication, not a supplement.</t>
+          <t>Mentions 'SERTRALINE TABLETS', which is a medication, excluded.</t>
         </is>
       </c>
     </row>
@@ -10532,7 +10532,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>Ingestion of an unspecified pill without mention of vitamin or dietary supplement, and no indication of iron content.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -10634,11 +10634,11 @@
         <v>1</v>
       </c>
       <c r="AA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>Mentions 'CHILDREN'S CHEWABLE ***' which is a supplement without specifying iron content.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -10740,11 +10740,11 @@
         <v>1</v>
       </c>
       <c r="AA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>Mentions 'melatonin' (supplement; no iron) and explicitly states 'accidental ingestion of melatonin'.</t>
+          <t>Hard Rule: Mentions melatonin (non-vitamin supplement).</t>
         </is>
       </c>
     </row>
@@ -10850,7 +10850,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>No explicit mention of vitamin or dietary supplement; ingestion alone does not imply label=1</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -10956,7 +10956,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>Mentions 'diet pills' which are supplements, but does not specify if they contain iron; also mentions 'ingestion of unknown amount'</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -11062,7 +11062,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>Mentions 'pill' without specifying supplement or medication, and does not mention iron.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -11167,7 +11167,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>Mentions 'meds' which implies prescription medication, not a supplement.</t>
+          <t>Mentions 'MEDS' which refers to medications, excluded.</t>
         </is>
       </c>
     </row>
@@ -11273,7 +11273,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>Hydrogen peroxide is a household chemical/toxin, not a supplement.</t>
+          <t>Ingestion of 'hydrogen peroxide' is a household chemical/toxin, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>Daily pills are not explicitly stated as supplements; mentions 'pills' which could be medication.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -11517,7 +11517,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements, and mentions 'antibiotics' which are medications.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -11627,7 +11627,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>Mentions 'caustic substance' which is a household chemical/toxin, not a supplement.</t>
+          <t>Ingestion of 'patco grease relief' is a household chemical/toxin, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -11733,7 +11733,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>No explicit mention of a vitamin or supplement; only an accidental overdose with no clear substance mentioned.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -11851,7 +11851,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>Bleach is a household chemical, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -11957,7 +11957,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>No explicit mention of a vitamin or supplement, and presence of 'laundry detergent' which is a chemical.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -12063,7 +12063,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>Mentions 'blood pressure meds' which are prescription medications, not supplements.</t>
+          <t>Mentions 'BLOOD PRESSURE MEDS: DOXAZOSIN', which is a medication, excluded.</t>
         </is>
       </c>
     </row>
@@ -12169,7 +12169,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements, only intoxication and physical injury.</t>
+          <t>Narrative does not mention any specific vitamin, fish oil, or vitamin C/D/etc., and does not involve any ingestions.</t>
         </is>
       </c>
     </row>
@@ -12275,7 +12275,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>Liquid nicotine cartridge is a household chemical/toxin, not a supplement.</t>
+          <t>Ingestion of a nicotine cartridge, which is a chemical/toxin, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -12381,7 +12381,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>Bleach is a household chemical, not a supplement.</t>
+          <t>Mentions 'BLEACH', which is a household chemical/toxin, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -12491,7 +12491,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>No explicit mention of vitamin or supplement ingestion.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -12597,7 +12597,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>Stain remover is a household chemical, not a supplement.</t>
+          <t>Ingestion of 'stain remover' is a household chemical, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -12703,7 +12703,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>Mentions 'rubbing alcohol' which is a household chemical, not a supplement.</t>
+          <t>Ingestion of 'rubbing alcohol' which is a household chemical/toxin, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -12825,7 +12825,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>Mentions 'birth control pills' which are medication, not supplements.</t>
+          <t>Mentions 'birth control pills' and specific medications (noregestimate and ethinyl estradiol), which are excluded.</t>
         </is>
       </c>
     </row>
@@ -12931,7 +12931,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>No mention of vitamin or dietary supplement; only mentions 'Talbet' which is an unknown substance.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -13037,7 +13037,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>Perfume is a household chemical, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -13143,7 +13143,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>No explicit mention of vitamin or dietary supplement; ingestion alone does not imply label=1</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -13249,7 +13249,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>No explicit mention of vitamin or dietary supplement; ingestion is possible but substance unknown.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -13367,7 +13367,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>Laundry soap pod is a household chemical, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -13477,7 +13477,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>Mentions 'essential oil' which is not a supplement, but a household chemical.</t>
+          <t>Mentions 'essential oil' which is a household chemical/toxin, not a specified vitamin or fish oil.</t>
         </is>
       </c>
     </row>
@@ -13607,7 +13607,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements; mentions 'bowel prep' which is a medication for colonoscopy.</t>
+          <t>Narrative describes bowel prep for colonoscopy and syncope, with no mention of any vitamin or vitamin supplement.</t>
         </is>
       </c>
     </row>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements, only 'nitrous oxide' which is a chemical.</t>
+          <t>Narrative describes nitrous oxide inhalation, which is a chemical/gas, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -13839,7 +13839,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements, and no indication of iron-containing formulation.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -13953,11 +13953,11 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>Mentions 'marijuana gummies' which are supplements, but no iron mentioned.</t>
+          <t>Hard Rule: Mentions cannabis product.</t>
         </is>
       </c>
     </row>
@@ -14063,7 +14063,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>Mentions 'pills' without specifying supplement or medication; no indication of vitamin/supplement ingestion.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -14169,7 +14169,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>Mentions 'perfume' which is a household chemical/toxin, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -14303,7 +14303,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements in the narrative.</t>
+          <t>Narrative describes an accident and intoxication, with no mention of vitamin ingestion.</t>
         </is>
       </c>
     </row>
@@ -14409,7 +14409,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>Air freshener is a household chemical/toxin, not a supplement.</t>
+          <t>Narrative describes exposure to an air freshener, not a vitamin or vitamin supplement.</t>
         </is>
       </c>
     </row>
@@ -14527,7 +14527,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>Gliptizide is a prescription medication, not a supplement.</t>
+          <t>Mentions 'Gliipizide pills', which is a medication, excluded.</t>
         </is>
       </c>
     </row>
@@ -14633,7 +14633,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>Toilet bowl cleaner is a household chemical, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -14739,7 +14739,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>Laundry detergent is a chemical, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -14845,7 +14845,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>Mentions '*** pills' which does not specify a vitamin/supplement, and no iron is mentioned but the formulation is unknown.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -14951,7 +14951,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>Neither 'vodka' nor 'commercial computer dusting spray' are supplements.</t>
+          <t>Ingestion of 'vodka' and 'computer dusting spray' are household chemicals/toxins, not vitamins.</t>
         </is>
       </c>
     </row>
@@ -15057,7 +15057,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements, only household chemical 'bubbles' (bubble liquid).</t>
+          <t>The narrative describes ingestion of 'bubble liquid', which is a household substance, not a specified vitamin or fish oil.</t>
         </is>
       </c>
     </row>
@@ -15163,7 +15163,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements; mentions prescription medication 'metoprolol' and accidental ingestion.</t>
+          <t>Mentions 'METOPROLOL' which is a medication, excluded.</t>
         </is>
       </c>
     </row>
@@ -15269,7 +15269,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>Mentions 'melatonin' (supplement; no iron) but with unclear formulation ('*** MELATONINDX POISON')</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -15375,7 +15375,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>Mentions iron formulation (e.g., 'iron/Fe/ferrous'); iron-containing products are excluded.</t>
+          <t>Hard Rule: Mentions iron formulation.</t>
         </is>
       </c>
     </row>
@@ -15493,7 +15493,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements, and peppermint oil is a household chemical.</t>
+          <t>Mentions 'peppermint oil' which is a household substance/oil, not a specified vitamin or fish oil.</t>
         </is>
       </c>
     </row>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements; mentions 'alcohol poisoning' which is a toxic ingestion.</t>
+          <t>Narrative describes alcohol poisoning and does not mention any vitamin or fish oil.</t>
         </is>
       </c>
     </row>
@@ -15705,7 +15705,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>Mentions 'bleach' which is a household chemical, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -15811,7 +15811,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>No explicit mention of a vitamin or supplement, and 'iron' is not mentioned.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -15917,7 +15917,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>Mentions 'tablet' without specifying supplement/vitamin content, and does not exclude iron-containing formulation.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -16023,7 +16023,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements; narrative mentions alcohol intoxication.</t>
+          <t>Narrative discusses alcohol ('LIQUR') and intoxication, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -16129,7 +16129,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements, but mentions household chemical 'bleach'.</t>
+          <t>Narrative describes exposure to household chemical 'BLEACH', not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -16235,7 +16235,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>Mentions '*** tabs' which does not explicitly indicate a vitamin or dietary supplement, and no iron-containing formulation is mentioned.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -16341,7 +16341,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements, only wine ingestion.</t>
+          <t>Narrative mentions 'wine' and does not involve a vitamin, fish oil, or explicitly safe vitamin.</t>
         </is>
       </c>
     </row>
@@ -16459,7 +16459,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>Mentions 'amoxicillin' which is an antibiotic, not a supplement.</t>
+          <t>Mentions 'AMOXICILLIN', which is a prescription medication, excluded.</t>
         </is>
       </c>
     </row>
@@ -16565,7 +16565,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>Mentions 'laxative' which is a medication, not a supplement.</t>
+          <t>Mentions 'laxative', which is a non-vitamin/non-specified substance, excluded.</t>
         </is>
       </c>
     </row>
@@ -16671,7 +16671,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>Mentions 'cleaning fluid' which is a household chemical, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -16777,7 +16777,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>Bleach is a household chemical, not a supplement.</t>
+          <t>Ingestion of household chemical 'bleach', not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -16883,7 +16883,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>No explicit mention of vitamin or dietary supplement; ingestion alone does not imply label=1.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -16997,11 +16997,11 @@
         <v>1</v>
       </c>
       <c r="AA151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>Mentions 'melatonin gummies' (supplement; no iron).</t>
+          <t>Hard Rule: Mentions melatonin (non-vitamin supplement).</t>
         </is>
       </c>
     </row>
@@ -17107,7 +17107,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>No mention of vitamin or dietary supplement; unclear if topical ointment was ingested.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -17217,7 +17217,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>Hand sanitizer is a household chemical, not a supplement.</t>
+          <t>Ingestion of hand sanitizer/household chemical, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements, only household chemical (glass cabinet) and ethanol intoxication.</t>
+          <t>Narrative describes alcohol intoxication and laceration, with no mention of a vitamin or fish oil.</t>
         </is>
       </c>
     </row>
@@ -17449,7 +17449,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>Fuel injector cleaner is a household chemical, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -17555,7 +17555,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>Glyburide is a prescription medication, not a supplement.</t>
+          <t>Mentions 'GLYBURIDE TABLETS', which is a medication, excluded.</t>
         </is>
       </c>
     </row>
@@ -17661,7 +17661,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>No explicit mention of a vitamin or supplement; ingestion is not sufficient to imply label=1.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -17767,7 +17767,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements; narrative mentions alcohol intoxication and fall.</t>
+          <t>Narrative describes alcohol intoxication and fall, with no mention of vitamins or specified ingestions.</t>
         </is>
       </c>
     </row>
@@ -17885,7 +17885,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>Mentions 'toxic substance' which is not a supplement, but rather a household chemical.</t>
+          <t>Ingestion of 'gun cleaner' is a household chemical/toxin, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -17991,7 +17991,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>Mentions 'DIET PILL' which is a type of supplement, but does not specify if it contains iron.</t>
+          <t>Hard Rule: Mentions weight-loss/diet supplement.</t>
         </is>
       </c>
     </row>
@@ -18097,7 +18097,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>No explicit mention of vitamin or dietary supplement; ingestion alone does not imply label=1</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -18207,7 +18207,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements; narrative is about alcohol intoxication.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -18313,7 +18313,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>Cough medicine is medication, not a supplement.</t>
+          <t>Mentions 'cough med', which is a medication and excluded.</t>
         </is>
       </c>
     </row>
@@ -18431,7 +18431,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>Pedialax is an OTC medication, not a supplement.</t>
+          <t>Mentions 'liquid medicine' and 'suppository', which are excluded categories.</t>
         </is>
       </c>
     </row>
@@ -18549,7 +18549,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements.</t>
+          <t>Narrative describes exposure to latex paint, not a vitamin or vitamin supplement.</t>
         </is>
       </c>
     </row>
@@ -18651,11 +18651,11 @@
         <v>1</v>
       </c>
       <c r="AA166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>Mentions 'cholesterol formula' / 'diet supplement', which are supplements without iron.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -18761,7 +18761,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>Cannot determine if substance is a vitamin/supplement; '***' is unknown</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -18867,7 +18867,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>Mentions 'industrial cleaner' which is a household chemical, not a supplement.</t>
+          <t>Narrative describes inhalation of household chemicals ('industrial cleaner fumes'), not a vitamin ingestion.</t>
         </is>
       </c>
     </row>
@@ -18977,7 +18977,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements.</t>
+          <t>Narrative describes alcohol intoxication, not vitamin ingestion.</t>
         </is>
       </c>
     </row>
@@ -19087,7 +19087,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>Mentions 'NORVASE' which is an OTC medication, not a supplement.</t>
+          <t>Mentions 'NORVASE' which is a medication, excluded.</t>
         </is>
       </c>
     </row>
@@ -19197,7 +19197,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -19303,7 +19303,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>No explicit mention of a vitamin or supplement, and the substance is unknown.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -19433,7 +19433,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements; substance abuse diagnosis implies ingestion of illicit substances.</t>
+          <t>Narrative describes 'DRUG UNK' and 'SUBSTANCE ABUSE' without specifying a pure, non-iron vitamin or fish oil.</t>
         </is>
       </c>
     </row>
@@ -19551,7 +19551,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>Mentions 'INGESTION OF UNKNOWN MEDS' which implies medication, not a supplement.</t>
+          <t>Mentions multiple medications (hydrochlorothiazide, cyclobenzaprine, propranolol), which are excluded.</t>
         </is>
       </c>
     </row>
@@ -19657,7 +19657,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements; narrative mentions 'etoh' (ethanol) which is a household chemical/toxin.</t>
+          <t>Narrative mentions 'ETOH' (ethanol/alcohol) intoxication, which is not a vitamin or fish oil.</t>
         </is>
       </c>
     </row>
@@ -19763,7 +19763,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>Aspirin is an OTC medication, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -19869,7 +19869,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements, only an allergic reaction to a bee sting.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -19983,11 +19983,11 @@
         <v>1</v>
       </c>
       <c r="AA178" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>Mentions 'CBD gummy' which is a supplement without iron.</t>
+          <t>Hard Rule: Mentions cannabis product.</t>
         </is>
       </c>
     </row>
@@ -20093,7 +20093,7 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements; only mentions 'ETOH' (ethanol) which is a household chemical/toxin, not a supplement.</t>
+          <t>Narrative describes alcohol intoxication, not vitamin ingestion.</t>
         </is>
       </c>
     </row>
@@ -20199,7 +20199,7 @@
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>Chemical inhalation due to bleach and ammonia exposure; not a supplement ingestion.</t>
+          <t>Involves chemical inhalation (bleach and ammonia) and not a vitamin/fish oil ingestion.</t>
         </is>
       </c>
     </row>
@@ -20305,7 +20305,7 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>Mentions 'toxic medication exposure' which implies prescription or OTC medication, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -20411,7 +20411,7 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>Gabapentin is an OTC medication, not a supplement.</t>
+          <t>Mentions 'GABAPENTIN PILL', which is a medication, excluded.</t>
         </is>
       </c>
     </row>
@@ -20517,7 +20517,7 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements; narrative is about alcohol intoxication.</t>
+          <t>Narrative describes alcohol intoxication, not vitamin ingestion.</t>
         </is>
       </c>
     </row>
@@ -20623,7 +20623,7 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements; mentions '***' which is likely a medication for eczema.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -20729,7 +20729,7 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>No explicit mention of a vitamin or supplement; ingestion is unclear.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -20835,7 +20835,7 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>Pillbox contents are not specified as supplements or vitamins, and 'iron' is not mentioned.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -20941,7 +20941,7 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements; heroin is an illicit substance.</t>
+          <t>Mentions 'HEROIN', which is a drug/toxin, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -21047,7 +21047,7 @@
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>Mentions '***' which implies an unknown substance, and does not explicitly mention a vitamin or dietary supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -21165,7 +21165,7 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>Bleach is a household chemical, not a supplement.</t>
+          <t>Involves exposure to household chemical 'BLEACH', not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -21271,7 +21271,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements; only inhalation and chest pain symptoms.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -21377,7 +21377,7 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements; narrative mentions ethanol intoxication instead.</t>
+          <t>Narrative describes ethanol intoxication and is unrelated to vitamin ingestion.</t>
         </is>
       </c>
     </row>
@@ -21479,11 +21479,11 @@
         <v>1</v>
       </c>
       <c r="AA192" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>Mentions 'fish oil pills' which are supplements without iron.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -21589,7 +21589,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>No explicit mention of vitamin or dietary supplement, and 'iron' is not mentioned.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -21695,7 +21695,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>No explicit mention of a vitamin or supplement, and mentions 'pill box' which implies prescription medication.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -21801,7 +21801,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>No explicit mention of vitamin or dietary supplement; ingestion alone does not imply label=1</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -21907,7 +21907,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>No explicit mention of vitamin or supplement ingestion.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -22025,7 +22025,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>Ingestion of 'toxic substance' implies unknown or non-supplement ingestion, and does not explicitly mention a vitamin/supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -22131,7 +22131,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>No mention of vitamin or supplement ingestion, only exposure to bathroom cleaner.</t>
+          <t>Narrative describes exposure to household cleaner vapors, not a vitamin ingestion.</t>
         </is>
       </c>
     </row>
@@ -22261,7 +22261,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements.</t>
+          <t>Narrative describes alcohol intoxication and does not mention any vitamin or fish oil.</t>
         </is>
       </c>
     </row>
@@ -22367,7 +22367,7 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>No explicit mention of a vitamin or supplement; ingestion is to '*** tablets' which could be medication.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -22473,7 +22473,7 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>Mentions 'PRENATAL VITAMINS WITH IRON' -&gt; iron-containing formulation is excluded.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -22591,7 +22591,7 @@
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>No explicit mention of a vitamin or supplement, and 'diarrhea pills' could be medication.</t>
+          <t>Mentions 'diarrhea pills' which is a non-vitamin supplement, and the ingestion is uncertain/ambiguous.</t>
         </is>
       </c>
     </row>
@@ -22697,7 +22697,7 @@
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>Torch oil is a household chemical, not a supplement.</t>
+          <t>Mentions 'TORCH OIL' which is a household chemical/toxin, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -22803,7 +22803,7 @@
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements; only ethanol intoxication mentioned.</t>
+          <t>Narrative mentions 'ETOH' (ethanol/alcohol) intoxication, which is not a vitamin, and does not mention any vitamin or fish oil.</t>
         </is>
       </c>
     </row>
@@ -22909,7 +22909,7 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>Household bleach is a toxic chemical, not a supplement.</t>
+          <t>Mentions 'household bleach', which is a chemical toxin, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -23015,7 +23015,7 @@
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>SILICA GEL is a household chemical, not a supplement.</t>
+          <t>Mentions 'silica gel packet', which is a household chemical/toxin, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -23121,7 +23121,7 @@
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements.</t>
+          <t>Narrative describes alcohol intoxication, not vitamin ingestion.</t>
         </is>
       </c>
     </row>
@@ -23227,7 +23227,7 @@
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>Dishwashing detergent is a household chemical, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -23333,7 +23333,7 @@
       </c>
       <c r="AB209" t="inlineStr">
         <is>
-          <t>Mentions iron formulation (e.g., 'iron/Fe/ferrous'); iron-containing products are excluded.</t>
+          <t>Hard Rule: Mentions iron formulation.</t>
         </is>
       </c>
     </row>
@@ -23439,7 +23439,7 @@
       </c>
       <c r="AB210" t="inlineStr">
         <is>
-          <t>Mentions 'steam cough suppressant' which is a medication, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -23545,7 +23545,7 @@
       </c>
       <c r="AB211" t="inlineStr">
         <is>
-          <t>Mentions iron formulation (e.g., 'iron/Fe/ferrous'); iron-containing products are excluded.</t>
+          <t>Hard Rule: Mentions iron formulation.</t>
         </is>
       </c>
     </row>
@@ -23651,7 +23651,7 @@
       </c>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>Mentions 'TABLETS' without specifying supplement or medication, defaulting to label=0.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -23769,7 +23769,7 @@
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>No explicit mention of a vitamin or supplement, and the substance is unknown.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -23879,7 +23879,7 @@
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>No mention of vitamins or dietary supplements.</t>
+          <t>Narrative discusses opiate intoxication and bee sting, with no mention of a strictly harmless vitamin or fish oil.</t>
         </is>
       </c>
     </row>
@@ -23997,7 +23997,7 @@
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>No explicit mention of vitamin or dietary supplement; ingestion could be any substance.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -24115,7 +24115,7 @@
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>Mentions 'drug ingestion' which implies medication, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -24221,7 +24221,7 @@
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>No specific substance mentioned; cannot determine if it's a vitamin/supplement or not.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -24331,7 +24331,7 @@
       </c>
       <c r="AB218" t="inlineStr">
         <is>
-          <t>Mentions 'amoxicillin' which is an antibiotic medication, not a supplement.</t>
+          <t>Mentions 'AMOXICILLAN', which is a medication, excluded.</t>
         </is>
       </c>
     </row>
@@ -24437,7 +24437,7 @@
       </c>
       <c r="AB219" t="inlineStr">
         <is>
-          <t>Bleach is a household chemical, not a supplement.</t>
+          <t>Mentions 'BLEACH', which is a household chemical/toxin, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -24543,7 +24543,7 @@
       </c>
       <c r="AB220" t="inlineStr">
         <is>
-          <t>Mentions 'Drama-Mine' which is a medication, not a supplement.</t>
+          <t>Mentions 'meclizine' and 'drama-mine', which are medications, excluded.</t>
         </is>
       </c>
     </row>
@@ -24661,7 +24661,7 @@
       </c>
       <c r="AB221" t="inlineStr">
         <is>
-          <t>Mentions iron formulation (e.g., 'iron/Fe/ferrous'); iron-containing products are excluded.</t>
+          <t>Hard Rule: Mentions iron formulation.</t>
         </is>
       </c>
     </row>
@@ -24779,7 +24779,7 @@
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>Enalapril is a prescription medication, not a supplement.</t>
+          <t>Mentions 'ENALAPRIL', which is a medication, excluded.</t>
         </is>
       </c>
     </row>
@@ -24897,7 +24897,7 @@
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>No explicit mention of a vitamin or supplement, and no iron-containing formulation mentioned.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -25027,7 +25027,7 @@
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements.</t>
+          <t>Narrative describes fall and low blood sugar, but does not mention any vitamin, fish oil, or vitamin C/D/etc. It mentions 'METFORMIN', which is a medication.</t>
         </is>
       </c>
     </row>
@@ -25133,7 +25133,7 @@
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements; narrative focuses on dehydration and unresponsiveness.</t>
+          <t>No mention of any specific vitamin, fish oil, or acceptable supplement.</t>
         </is>
       </c>
     </row>
@@ -25243,7 +25243,7 @@
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements.</t>
+          <t>Narrative describes a reaction but does not mention any specific vitamin, fish oil, or vitamin product ingestion.</t>
         </is>
       </c>
     </row>
@@ -25349,7 +25349,7 @@
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>No explicit mention of vitamin or supplement, and 'tabs' could refer to medication.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -25455,7 +25455,7 @@
       </c>
       <c r="AB228" t="inlineStr">
         <is>
-          <t>Cough syrup is medication, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -25561,7 +25561,7 @@
       </c>
       <c r="AB229" t="inlineStr">
         <is>
-          <t>Mentions 'Amlodipine' which is a prescription medication, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -25667,7 +25667,7 @@
       </c>
       <c r="AB230" t="inlineStr">
         <is>
-          <t>Mentions '*** tablets' which could be medication or household chemicals; no clear indication of vitamin/supplement ingestion</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -25773,7 +25773,7 @@
       </c>
       <c r="AB231" t="inlineStr">
         <is>
-          <t>No mention of vitamins or dietary supplements.</t>
+          <t>Narrative discusses cocaine use and chest pain, with no mention of a vitamin or fish oil.</t>
         </is>
       </c>
     </row>
@@ -25879,7 +25879,7 @@
       </c>
       <c r="AB232" t="inlineStr">
         <is>
-          <t>Mentions 'COME CLEANER' which is a household chemical/toxin, not a supplement.</t>
+          <t>Mentions 'cleaner', which is a household chemical/toxin, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -26009,7 +26009,7 @@
       </c>
       <c r="AB233" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements, and treatment for COVID-19 is medication.</t>
+          <t>Narrative describes medical history and symptoms, with no mention of vitamin or vitamin-containing product ingestion.</t>
         </is>
       </c>
     </row>
@@ -26115,7 +26115,7 @@
       </c>
       <c r="AB234" t="inlineStr">
         <is>
-          <t>Mentions 'methotrexate' which is a medication, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -26233,7 +26233,7 @@
       </c>
       <c r="AB235" t="inlineStr">
         <is>
-          <t>No explicit mention of a vitamin or supplement, and no iron-containing formulation mentioned.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -26343,7 +26343,7 @@
       </c>
       <c r="AB236" t="inlineStr">
         <is>
-          <t>Mentions 'meds' which are likely prescription medications, not supplements.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -26449,7 +26449,7 @@
       </c>
       <c r="AB237" t="inlineStr">
         <is>
-          <t>No mention of vitamin or dietary supplement; mentions prescription medication 'clonazepam'.</t>
+          <t>Mentions 'CLONAZEPAM' which is a medication, excluded.</t>
         </is>
       </c>
     </row>
@@ -26555,7 +26555,7 @@
       </c>
       <c r="AB238" t="inlineStr">
         <is>
-          <t>No explicit mention of vitamin or dietary supplement; ingestion is unknown substance.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -26661,7 +26661,7 @@
       </c>
       <c r="AB239" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements; substance abuse is too vague to imply a vitamin/supplement ingestion.</t>
+          <t>Narrative mentions 'SUBSTANCE ABUSE' without specifying a vitamin, and no specific vitamin or fish oil is mentioned.</t>
         </is>
       </c>
     </row>
@@ -26791,7 +26791,7 @@
       </c>
       <c r="AB240" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements.</t>
+          <t>Narrative describes alcohol abuse and intoxication, not vitamin ingestion.</t>
         </is>
       </c>
     </row>
@@ -26909,7 +26909,7 @@
       </c>
       <c r="AB241" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements; narrative mentions medication and alcohol as contributing factors.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -27027,7 +27027,7 @@
       </c>
       <c r="AB242" t="inlineStr">
         <is>
-          <t>Mentions 'toxin ingestion' which implies a non-supplement substance was ingested.</t>
+          <t>Mentions 'Topiramate', which is a medication, excluded.</t>
         </is>
       </c>
     </row>
@@ -27133,7 +27133,7 @@
       </c>
       <c r="AB243" t="inlineStr">
         <is>
-          <t>Mentions 'laundry detergent' which is a household chemical, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -27239,7 +27239,7 @@
       </c>
       <c r="AB244" t="inlineStr">
         <is>
-          <t>Pills mentioned are medications (Clondine, Carveciol, Gabapentin) not supplements.</t>
+          <t>Mentions multiple medications (Clonidine, Carvecilol, Gabapentin), which are excluded.</t>
         </is>
       </c>
     </row>
@@ -27345,7 +27345,7 @@
       </c>
       <c r="AB245" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements.</t>
+          <t>No mention of any vitamin, fish oil, or acceptable supplement.</t>
         </is>
       </c>
     </row>
@@ -27451,7 +27451,7 @@
       </c>
       <c r="AB246" t="inlineStr">
         <is>
-          <t>Cefdinir is an antibiotic medication, not a supplement.</t>
+          <t>Mentions 'CEFDINIR' which is a medication, excluded.</t>
         </is>
       </c>
     </row>
@@ -27557,7 +27557,7 @@
       </c>
       <c r="AB247" t="inlineStr">
         <is>
-          <t>Mentions 'detergent' which is a household chemical, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -27663,7 +27663,7 @@
       </c>
       <c r="AB248" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements; chest pain diagnosis and hypercholesterolemia are unrelated to vitamin/supplement ingestion.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -27785,7 +27785,7 @@
       </c>
       <c r="AB249" t="inlineStr">
         <is>
-          <t>No mention of vitamins or dietary supplements; exposure to industrial fumes is a chemical/toxin.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -27903,7 +27903,7 @@
       </c>
       <c r="AB250" t="inlineStr">
         <is>
-          <t>Labetalol is a prescription medication, not a supplement.</t>
+          <t>Mentions 'LABETALOL TABLET', which is a medication, excluded.</t>
         </is>
       </c>
     </row>
@@ -28009,7 +28009,7 @@
       </c>
       <c r="AB251" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements in the narrative.</t>
+          <t>Narrative describes seizure activity and hypoglycemia related to insulin pump, containing no mention of vitamins or acceptable supplements.</t>
         </is>
       </c>
     </row>
@@ -28115,7 +28115,7 @@
       </c>
       <c r="AB252" t="inlineStr">
         <is>
-          <t>Accidental ingestion of *** implies unknown substance, and no mention of vitamin or supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -28221,7 +28221,7 @@
       </c>
       <c r="AB253" t="inlineStr">
         <is>
-          <t>No explicit mention of a vitamin or supplement; '***S' is unclear.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -28327,7 +28327,7 @@
       </c>
       <c r="AB254" t="inlineStr">
         <is>
-          <t>Mentions 'METOPRALOL' which is a prescription medication, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -28433,7 +28433,7 @@
       </c>
       <c r="AB255" t="inlineStr">
         <is>
-          <t>No explicit mention of a vitamin or supplement, and 'iron' is not mentioned.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -28539,7 +28539,7 @@
       </c>
       <c r="AB256" t="inlineStr">
         <is>
-          <t>Mentions 'multiple meds' which implies prescription medication, not a supplement.</t>
+          <t>Mentions 'MULTIPLE MEDS' and is ambiguous, triggering exclusion rules for unknown medications.</t>
         </is>
       </c>
     </row>
@@ -28645,7 +28645,7 @@
       </c>
       <c r="AB257" t="inlineStr">
         <is>
-          <t>No explicit mention of vitamin or dietary supplement; ingestion is unknown.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -28751,7 +28751,7 @@
       </c>
       <c r="AB258" t="inlineStr">
         <is>
-          <t>Ingestion of unknown substance *** without explicit mention of vitamin or dietary supplement</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -28869,7 +28869,7 @@
       </c>
       <c r="AB259" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements; ingestion is to tobacco salt from vape pen.</t>
+          <t>Mentions 'tobacco salt' and 'vape pen', which are not vitamins or fish oil.</t>
         </is>
       </c>
     </row>
@@ -28975,7 +28975,7 @@
       </c>
       <c r="AB260" t="inlineStr">
         <is>
-          <t>Paint is a household chemical/toxin, not a supplement.</t>
+          <t>Ingestion of 'paint' is a household chemical/toxin, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -29081,7 +29081,7 @@
       </c>
       <c r="AB261" t="inlineStr">
         <is>
-          <t>Hydralazine is an OTC medication, not a supplement.</t>
+          <t>Mentions 'HYDRALAZINE 50MG TAB', which is a medication, excluded.</t>
         </is>
       </c>
     </row>
@@ -29187,7 +29187,7 @@
       </c>
       <c r="AB262" t="inlineStr">
         <is>
-          <t>Gabapentin is a prescription medication, not a supplement.</t>
+          <t>Mentions 'GABAPENTIN', which is a medication, excluded.</t>
         </is>
       </c>
     </row>
@@ -29293,7 +29293,7 @@
       </c>
       <c r="AB263" t="inlineStr">
         <is>
-          <t>Bleach is a household chemical, not a supplement.</t>
+          <t>Mentions 'BLEACH', which is a household chemical/toxin, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -29399,7 +29399,7 @@
       </c>
       <c r="AB264" t="inlineStr">
         <is>
-          <t>Mentions 'pill container' with 'STOOL SOFTENER' which is a medication, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -29505,7 +29505,7 @@
       </c>
       <c r="AB265" t="inlineStr">
         <is>
-          <t>Mentions 'drug ingestion' which is not a supplement, and also mentions opiates which are medication.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -29611,7 +29611,7 @@
       </c>
       <c r="AB266" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements, and ingestion is unclear.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -29737,7 +29737,7 @@
       </c>
       <c r="AB267" t="inlineStr">
         <is>
-          <t>Mentions 'laundry detergent' which is a chemical, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -29843,7 +29843,7 @@
       </c>
       <c r="AB268" t="inlineStr">
         <is>
-          <t>Ingestion alone does NOT imply label=1; no explicit mention of vitamin/supplement</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -29949,7 +29949,7 @@
       </c>
       <c r="AB269" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements.</t>
+          <t>Narrative describes a laceration and INR, with no mention of vitamin ingestion.</t>
         </is>
       </c>
     </row>
@@ -30055,7 +30055,7 @@
       </c>
       <c r="AB270" t="inlineStr">
         <is>
-          <t>Mentions 'medications' which are not supplements, and does not specify a vitamin or dietary supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -30173,7 +30173,7 @@
       </c>
       <c r="AB271" t="inlineStr">
         <is>
-          <t>Mentions 'LAWN WORK PROJECT' and 'FUMES FROM LAWN WORK PROJECT', which implies exposure to a chemical/toxin (lead compounds) rather than a supplement.</t>
+          <t>Narrative describes poisoning by lead fumes, not ingestion of a vitamin.</t>
         </is>
       </c>
     </row>
@@ -30279,7 +30279,7 @@
       </c>
       <c r="AB272" t="inlineStr">
         <is>
-          <t>Mentions 'cleaner solution' which is a household chemical, not a supplement.</t>
+          <t>Ingestion of a household cleaner solution, which is a toxin, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -30397,7 +30397,7 @@
       </c>
       <c r="AB273" t="inlineStr">
         <is>
-          <t>Mentions 'bathroom cleaner' which is a household chemical, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -30503,7 +30503,7 @@
       </c>
       <c r="AB274" t="inlineStr">
         <is>
-          <t>Lamp oil is a household chemical, not a supplement.</t>
+          <t>Ingestion of 'lamp oil' is a household chemical/toxin, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -30613,7 +30613,7 @@
       </c>
       <c r="AB275" t="inlineStr">
         <is>
-          <t>Mentions 'antibiotic pills' which are medication, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -30723,7 +30723,7 @@
       </c>
       <c r="AB276" t="inlineStr">
         <is>
-          <t>Tramadol is an OTC medication, not a supplement.</t>
+          <t>Mentions 'TRAMADOL', which is a medication, excluded.</t>
         </is>
       </c>
     </row>
@@ -30829,7 +30829,7 @@
       </c>
       <c r="AB277" t="inlineStr">
         <is>
-          <t>SIAPERRASH cream is a topical medication, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -30947,7 +30947,7 @@
       </c>
       <c r="AB278" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements.</t>
+          <t>Narrative discusses medical history and chemotherapy, with no mention of vitamin ingestion.</t>
         </is>
       </c>
     </row>
@@ -31053,7 +31053,7 @@
       </c>
       <c r="AB279" t="inlineStr">
         <is>
-          <t>No explicit mention of vitamin or dietary supplement; '***' indicates unknown substance</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -31171,7 +31171,7 @@
       </c>
       <c r="AB280" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements in the narrative.</t>
+          <t>Narrative mentions 'PILLS' but does not specify a clear, traditional vitamin or fish oil, and is too ambiguous.</t>
         </is>
       </c>
     </row>
@@ -31297,7 +31297,7 @@
       </c>
       <c r="AB281" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements.</t>
+          <t>Narrative describes fall and intoxication, with no mention of vitamin ingestion.</t>
         </is>
       </c>
     </row>
@@ -31403,7 +31403,7 @@
       </c>
       <c r="AB282" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements; ingestion is a foreign body.</t>
+          <t>Narrative describes e-cigarette contents/foreign body, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -31521,7 +31521,7 @@
       </c>
       <c r="AB283" t="inlineStr">
         <is>
-          <t>Mentions 'Zinc Chloride' which is a household chemical, not a supplement.</t>
+          <t>Ingestion of a battery, which is a household chemical/toxin, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -31627,7 +31627,7 @@
       </c>
       <c r="AB284" t="inlineStr">
         <is>
-          <t>Mentions '***icillin' which is an antibiotic medication, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -31753,7 +31753,7 @@
       </c>
       <c r="AB285" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements; narrative is about ethanol intoxication and physical injury.</t>
+          <t>Narrative describes alcohol intoxication and trauma, with no mention of vitamins or specified safe supplements.</t>
         </is>
       </c>
     </row>
@@ -31859,7 +31859,7 @@
       </c>
       <c r="AB286" t="inlineStr">
         <is>
-          <t>Mentions '***' which is unknown and does not clearly indicate a vitamin/supplement, so defaulting to 0.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -31965,7 +31965,7 @@
       </c>
       <c r="AB287" t="inlineStr">
         <is>
-          <t>Unknown substance ingested; cannot confirm if it's a vitamin/supplement or not.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -32067,11 +32067,11 @@
         <v>1</v>
       </c>
       <c r="AA288" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB288" t="inlineStr">
         <is>
-          <t>Mentions 'Vitamin B12' which is a vitamin, but does not exclude iron; however, the narrative does not mention iron, so it could be a supplement without iron. However, since the amount of ingestion is unknown and it's a pill (which can sometimes imply medication), I will err on the side of caution and choose 0.</t>
+          <t>Explicit 'vitamin B12' ingestion, which is a pure vitamin and does not contain iron.</t>
         </is>
       </c>
     </row>
@@ -32177,7 +32177,7 @@
       </c>
       <c r="AB289" t="inlineStr">
         <is>
-          <t>No explicit mention of vitamin or supplement; pill is unidentified.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -32287,7 +32287,7 @@
       </c>
       <c r="AB290" t="inlineStr">
         <is>
-          <t>Ingestion of liquid without specifying substance type (e.g., vitamin/supplement) implies it may be a household chemical or medication, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -32405,7 +32405,7 @@
       </c>
       <c r="AB291" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements, only immunization reaction and fever.</t>
+          <t>The narrative describes an immunization reaction, not an ingestion of a vitamin.</t>
         </is>
       </c>
     </row>
@@ -32511,7 +32511,7 @@
       </c>
       <c r="AB292" t="inlineStr">
         <is>
-          <t>Mentions 'tabs' without specifying supplement content, so defaulting to label=0.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -32617,7 +32617,7 @@
       </c>
       <c r="AB293" t="inlineStr">
         <is>
-          <t>No mention of vitamins or dietary supplements.</t>
+          <t>Mentions 'CANNABINOIDS', which are cannabis products and are excluded.</t>
         </is>
       </c>
     </row>
@@ -32735,7 +32735,7 @@
       </c>
       <c r="AB294" t="inlineStr">
         <is>
-          <t>Mentions 'blood pressure pill' (prescription medication) and 'ingestion of foreign substance', which are not supplements.</t>
+          <t>Mentions 'blood pressure pill (NIFEDIPINE 30 MG)' which is a medication, excluded.</t>
         </is>
       </c>
     </row>
@@ -32845,7 +32845,7 @@
       </c>
       <c r="AB295" t="inlineStr">
         <is>
-          <t>Ingestion alone does NOT imply label=1; no explicit mention of vitamin/supplement</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -32951,7 +32951,7 @@
       </c>
       <c r="AB296" t="inlineStr">
         <is>
-          <t>Mentions 'rubbining alcohol' which is a household chemical, not a supplement.</t>
+          <t>Mentions 'rubbing alcohol' which is a household chemical/toxin, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -33057,7 +33057,7 @@
       </c>
       <c r="AB297" t="inlineStr">
         <is>
-          <t>Lighter fluid is a household chemical, not a supplement.</t>
+          <t>Narrative describes inhalation of lighter fluid, which is a household chemical/toxin, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -33159,11 +33159,11 @@
         <v>1</v>
       </c>
       <c r="AA298" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB298" t="inlineStr">
         <is>
-          <t>Mentions 'FAT LOSS PILLS' which are supplements without iron.</t>
+          <t>Hard Rule: Mentions weight-loss/diet supplement.</t>
         </is>
       </c>
     </row>
@@ -33269,7 +33269,7 @@
       </c>
       <c r="AB299" t="inlineStr">
         <is>
-          <t>Ingestion of an unspecified pill; no mention of vitamin or dietary supplement</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -33375,7 +33375,7 @@
       </c>
       <c r="AB300" t="inlineStr">
         <is>
-          <t>Mentions 'medication' and does not specify any vitamin/supplement, so defaulting to 0.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -33481,7 +33481,7 @@
       </c>
       <c r="AB301" t="inlineStr">
         <is>
-          <t>No explicit mention of a vitamin or supplement, and '***' is unknown.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -33599,7 +33599,7 @@
       </c>
       <c r="AB302" t="inlineStr">
         <is>
-          <t>Mentions 'STIMULANT' which is a medication, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -33729,7 +33729,7 @@
       </c>
       <c r="AB303" t="inlineStr">
         <is>
-          <t>No mention of vitamins or dietary supplements, only drug paraphernalia and unknown substance ingestion.</t>
+          <t>Narrative describes unknown substance use and drug paraphernalia, not a vitamin ingestion.</t>
         </is>
       </c>
     </row>
@@ -33847,7 +33847,7 @@
       </c>
       <c r="AB304" t="inlineStr">
         <is>
-          <t>Mentions 'med of ODT' which is an over-the-counter medication, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -33953,7 +33953,7 @@
       </c>
       <c r="AB305" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements.</t>
+          <t>Narrative describes alcohol intoxication and does not mention any vitamin or fish oil.</t>
         </is>
       </c>
     </row>
@@ -34059,7 +34059,7 @@
       </c>
       <c r="AB306" t="inlineStr">
         <is>
-          <t>Loratadine is an OTC medication, not a supplement.</t>
+          <t>Mentions 'loratidine', which is a medication, excluded.</t>
         </is>
       </c>
     </row>
@@ -34189,7 +34189,7 @@
       </c>
       <c r="AB307" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements.</t>
+          <t>Narrative discusses insulin and hypoglycemia, which are medications/conditions, not vitamin ingestion.</t>
         </is>
       </c>
     </row>
@@ -34295,7 +34295,7 @@
       </c>
       <c r="AB308" t="inlineStr">
         <is>
-          <t>Ingestion of 'liquid blend' without specifying supplement or vitamin content, and presence of 'foreign substance' implies it's not a known supplement.</t>
+          <t>The narrative describes a liquid blend for e-cigarettes, which is not a recognized vitamin or fish oil, and is considered a foreign substance.</t>
         </is>
       </c>
     </row>
@@ -34413,7 +34413,7 @@
       </c>
       <c r="AB309" t="inlineStr">
         <is>
-          <t>Bleach is a household chemical/toxin, not a supplement.</t>
+          <t>Mentions 'household bleach', which is a chemical toxin, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -34519,7 +34519,7 @@
       </c>
       <c r="AB310" t="inlineStr">
         <is>
-          <t>Citrarsol Natural Cleaner and Degreaser is a household chemical, not a supplement.</t>
+          <t>Ingestion of household cleaner/chemical, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -34625,7 +34625,7 @@
       </c>
       <c r="AB311" t="inlineStr">
         <is>
-          <t>Hair dye is a household chemical/toxin, not a supplement.</t>
+          <t>Ingestion of household chemical ('hair dye') is not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -34731,7 +34731,7 @@
       </c>
       <c r="AB312" t="inlineStr">
         <is>
-          <t>No explicit mention of vitamin or dietary supplement, and ingestion alone does not imply label=1.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -34837,7 +34837,7 @@
       </c>
       <c r="AB313" t="inlineStr">
         <is>
-          <t>No explicit mention of vitamin or dietary supplement; ingestion alone does not imply label=1.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -34955,7 +34955,7 @@
       </c>
       <c r="AB314" t="inlineStr">
         <is>
-          <t>Mentions 'drug ingestion' which is not a supplement, and does not specify vitamin/supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -35061,7 +35061,7 @@
       </c>
       <c r="AB315" t="inlineStr">
         <is>
-          <t>Mentions 'antifungal med' which is a medication, not a supplement.</t>
+          <t>Mentions 'ANTIFUNGAL MED', which is a medication, excluded.</t>
         </is>
       </c>
     </row>
@@ -35167,7 +35167,7 @@
       </c>
       <c r="AB316" t="inlineStr">
         <is>
-          <t>No specific substance mentioned; ingestion alone does NOT imply label=1</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -35285,7 +35285,7 @@
       </c>
       <c r="AB317" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements, only vaccines and medical treatment.</t>
+          <t>Narrative describes vaccine reaction and does not mention any vitamin, fish oil, or vitamin C.</t>
         </is>
       </c>
     </row>
@@ -35391,7 +35391,7 @@
       </c>
       <c r="AB318" t="inlineStr">
         <is>
-          <t>Mentions 'JET ALERT PILLS' which is a medication, not a supplement.</t>
+          <t>Narrative mentions 'OD JET ALERT PILLS' which is an unknown/ambiguous supplement, not a specified vitamin, and does not meet the criteria for label=1.</t>
         </is>
       </c>
     </row>
@@ -35497,7 +35497,7 @@
       </c>
       <c r="AB319" t="inlineStr">
         <is>
-          <t>Unknown substance ingested, no clear mention of vitamin or supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -35599,11 +35599,11 @@
         <v>1</v>
       </c>
       <c r="AA320" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB320" t="inlineStr">
         <is>
-          <t>Pills of 'Vit D3' are a vitamin supplement, but no iron is mentioned.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -35709,7 +35709,7 @@
       </c>
       <c r="AB321" t="inlineStr">
         <is>
-          <t>Ingestion of *** implies unknown substance; no explicit mention of vitamin or dietary supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -35815,7 +35815,7 @@
       </c>
       <c r="AB322" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements, only household chemical exposure.</t>
+          <t>Narrative describes exposure to heating oil, not a vitamin or fish oil.</t>
         </is>
       </c>
     </row>
@@ -35921,7 +35921,7 @@
       </c>
       <c r="AB323" t="inlineStr">
         <is>
-          <t>No explicit mention of a vitamin or supplement, and no indication that the pills were iron-containing.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -36051,7 +36051,7 @@
       </c>
       <c r="AB324" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements; narrative focuses on fall and medical conditions.</t>
+          <t>Narrative does not mention any vitamin, fish oil, or vitamin C/D/etc. It discusses fall and anemia.</t>
         </is>
       </c>
     </row>
@@ -36161,7 +36161,7 @@
       </c>
       <c r="AB325" t="inlineStr">
         <is>
-          <t>Fungicare is a household product, not a vitamin or dietary supplement.</t>
+          <t>Mentions 'Fungicare' which is an unknown/non-vitamin supplement, excluded.</t>
         </is>
       </c>
     </row>
@@ -36267,7 +36267,7 @@
       </c>
       <c r="AB326" t="inlineStr">
         <is>
-          <t>Mentions 'bath salts' which is often used to refer to synthetic cathinones, a type of illicit substance, not a vitamin or dietary supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -36373,7 +36373,7 @@
       </c>
       <c r="AB327" t="inlineStr">
         <is>
-          <t>IBUPROFEN is an OTC medication, not a supplement.</t>
+          <t>Mentions 'IBUPROFEN', which is a medication, excluded.</t>
         </is>
       </c>
     </row>
@@ -36479,7 +36479,7 @@
       </c>
       <c r="AB328" t="inlineStr">
         <is>
-          <t>No mention of vitamins or dietary supplements.</t>
+          <t>Hard Rule: Mentions cannabis product.</t>
         </is>
       </c>
     </row>
@@ -36585,7 +36585,7 @@
       </c>
       <c r="AB329" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements.</t>
+          <t>Narrative mentions medications (Gliipizide, Metformin) and no specific vitamin ingestion.</t>
         </is>
       </c>
     </row>
@@ -36691,7 +36691,7 @@
       </c>
       <c r="AB330" t="inlineStr">
         <is>
-          <t>Nail polish remover is a household chemical/toxin, not a supplement.</t>
+          <t>Ingestion of 'nail polish remover' which is a household chemical/toxin, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -36797,7 +36797,7 @@
       </c>
       <c r="AB331" t="inlineStr">
         <is>
-          <t>No explicit mention of vitamin or dietary supplement, and no indication of iron-containing formulation.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -36903,7 +36903,7 @@
       </c>
       <c r="AB332" t="inlineStr">
         <is>
-          <t>Mentions 'laundry detergent' which is a chemical/toxin, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -37005,11 +37005,11 @@
         <v>0</v>
       </c>
       <c r="AA333" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB333" t="inlineStr">
         <is>
-          <t>Mentions 'melatonin' which is a supplement without iron.</t>
+          <t>Hard Rule: Mentions melatonin (non-vitamin supplement).</t>
         </is>
       </c>
     </row>
@@ -37115,7 +37115,7 @@
       </c>
       <c r="AB334" t="inlineStr">
         <is>
-          <t>Mentions 'bleach' and 'cleaning solution', which are household chemicals, not supplements.</t>
+          <t>Ingestion of household chemical ('bleach &amp; cleaning solution') is not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -37221,7 +37221,7 @@
       </c>
       <c r="AB335" t="inlineStr">
         <is>
-          <t>No explicit mention of vitamin or dietary supplement; ingestion alone does not imply label=1</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -37327,7 +37327,7 @@
       </c>
       <c r="AB336" t="inlineStr">
         <is>
-          <t>Lip ointment is a household product, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -37433,7 +37433,7 @@
       </c>
       <c r="AB337" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements; only mentions 'shortness of breath' and 'edema', which are symptoms, not substances.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -37551,7 +37551,7 @@
       </c>
       <c r="AB338" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements, only medication (buspirone) and household item (jewelry box).</t>
+          <t>Mentions 'BUSPIRONE' which is a medication, excluded.</t>
         </is>
       </c>
     </row>
@@ -37657,7 +37657,7 @@
       </c>
       <c r="AB339" t="inlineStr">
         <is>
-          <t>Mentions 'drug ingestion' which is not a specific supplement/vitamin, and does not exclude iron.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -37767,7 +37767,7 @@
       </c>
       <c r="AB340" t="inlineStr">
         <is>
-          <t>Unknown pill ingestion; no explicit mention of vitamin or dietary supplement</t>
+          <t>The narrative mentions an 'unknown pill' and does not specify a clear, traditional vitamin or fish oil, triggering the ambiguous/unknown exclusion rule.</t>
         </is>
       </c>
     </row>
@@ -37873,7 +37873,7 @@
       </c>
       <c r="AB341" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements; narrative mentions illicit substances instead.</t>
+          <t>Narrative mentions 'COCAINE,HEROIN ABUSE' which are illicit substances, not vitamins.</t>
         </is>
       </c>
     </row>
@@ -38003,7 +38003,7 @@
       </c>
       <c r="AB342" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements.</t>
+          <t>Narrative describes alcohol intoxication and motor vehicle accident, with no mention of vitamin ingestion.</t>
         </is>
       </c>
     </row>
@@ -38109,7 +38109,7 @@
       </c>
       <c r="AB343" t="inlineStr">
         <is>
-          <t>Mentions 'marijuana' which is not a vitamin or dietary supplement.</t>
+          <t>Hard Rule: Mentions cannabis product.</t>
         </is>
       </c>
     </row>
@@ -38215,7 +38215,7 @@
       </c>
       <c r="AB344" t="inlineStr">
         <is>
-          <t>No mention of vitamin or dietary supplement; mentions 'for an ear infection' which implies prescription medication.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -38321,7 +38321,7 @@
       </c>
       <c r="AB345" t="inlineStr">
         <is>
-          <t>Gabapentin is an OTC medication, not a supplement.</t>
+          <t>Mentions 'gabapentin' which is a medication, excluded.</t>
         </is>
       </c>
     </row>
@@ -38427,7 +38427,7 @@
       </c>
       <c r="AB346" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements; mentions 'ink' which is a chemical, not a supplement.</t>
+          <t>Ingestion of ink from a pen is a household chemical/toxin, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -38533,7 +38533,7 @@
       </c>
       <c r="AB347" t="inlineStr">
         <is>
-          <t>Carpet cleaner is a household chemical, not a supplement.</t>
+          <t>Ingestion of 'carpet cleaner' is a household chemical, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -38651,7 +38651,7 @@
       </c>
       <c r="AB348" t="inlineStr">
         <is>
-          <t>Mentions 'medication' which is not a supplement, and does not contain key phrases indicating a vitamin or dietary supplement.</t>
+          <t>Mentions 'MEDICATION' which is too general and does not specify a pure vitamin or fish oil.</t>
         </is>
       </c>
     </row>
@@ -38757,7 +38757,7 @@
       </c>
       <c r="AB349" t="inlineStr">
         <is>
-          <t>Empty bottle and uncertainty about ingestion -&gt; cannot confirm supplement/vitamin ingestion.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -38867,7 +38867,7 @@
       </c>
       <c r="AB350" t="inlineStr">
         <is>
-          <t>Does not mention any specific vitamin or supplement; cannot determine if it's related to a vitamin/supplement ingestion.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -38977,7 +38977,7 @@
       </c>
       <c r="AB351" t="inlineStr">
         <is>
-          <t>No explicit mention of a vitamin or supplement, and 'ingestion' alone does not imply label=1.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -39083,7 +39083,7 @@
       </c>
       <c r="AB352" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements, and 'Peachy Whip' is an e-cigarette flavoring, not a supplement.</t>
+          <t>The narrative describes an unknown substance ('PEACHY WHIP') associated with cigarettes, not a specified vitamin or fish oil.</t>
         </is>
       </c>
     </row>
@@ -39189,7 +39189,7 @@
       </c>
       <c r="AB353" t="inlineStr">
         <is>
-          <t>No explicit mention of vitamin or supplement; breastfeeding is not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -39295,7 +39295,7 @@
       </c>
       <c r="AB354" t="inlineStr">
         <is>
-          <t>No mention of vitamins or dietary supplements.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -39401,7 +39401,7 @@
       </c>
       <c r="AB355" t="inlineStr">
         <is>
-          <t>No explicit mention of vitamin or dietary supplement; ingestion alone does not imply label=1.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -39507,7 +39507,7 @@
       </c>
       <c r="AB356" t="inlineStr">
         <is>
-          <t>Mentions 'medication' which is not a supplement, and does not specify vitamin/supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -39625,7 +39625,7 @@
       </c>
       <c r="AB357" t="inlineStr">
         <is>
-          <t>Mentions 'bleach' which is a household chemical, not a supplement.</t>
+          <t>Ingestion of bleach is a household chemical/toxin, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -39731,7 +39731,7 @@
       </c>
       <c r="AB358" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements; cannot determine if ingestion was related to a vitamin/supplement.</t>
+          <t>Narrative is too vague and does not mention any specific vitamin or acceptable supplement.</t>
         </is>
       </c>
     </row>
@@ -39837,7 +39837,7 @@
       </c>
       <c r="AB359" t="inlineStr">
         <is>
-          <t>No explicit mention of vitamin or dietary supplement; ingestion alone does not imply label=1</t>
+          <t>The narrative is highly ambiguous and does not specify a clear, traditional vitamin or fish oil, and contains redacted/unclear information.</t>
         </is>
       </c>
     </row>
@@ -39955,7 +39955,7 @@
       </c>
       <c r="AB360" t="inlineStr">
         <is>
-          <t>Mentions 'Hans Sanitizer' which is a household chemical, not a supplement.</t>
+          <t>Ingestion of 'sanitizer' is a household chemical/toxin, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -40061,7 +40061,7 @@
       </c>
       <c r="AB361" t="inlineStr">
         <is>
-          <t>Bleach is a household chemical, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -40167,7 +40167,7 @@
       </c>
       <c r="AB362" t="inlineStr">
         <is>
-          <t>Ingestion alone does NOT imply label=1; no explicit mention of vitamin/supplement</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -40273,7 +40273,7 @@
       </c>
       <c r="AB363" t="inlineStr">
         <is>
-          <t>Mentions 'DIET PILL' which is a medication, not a supplement.</t>
+          <t>Hard Rule: Mentions weight-loss/diet supplement.</t>
         </is>
       </c>
     </row>
@@ -40379,7 +40379,7 @@
       </c>
       <c r="AB364" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements; narrative mentions 'alcohol binge' and 'vomiting bags with white substance', which is likely related to alcohol ingestion.</t>
+          <t>Narrative describes alcohol ingestion and vomiting, with no mention of a strictly harmless vitamin or fish oil.</t>
         </is>
       </c>
     </row>
@@ -40485,7 +40485,7 @@
       </c>
       <c r="AB365" t="inlineStr">
         <is>
-          <t>Eye glass cleaner is a household chemical, not a supplement.</t>
+          <t>Ingestion of 'eyeglass cleaner' is a household chemical/toxin, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -40591,7 +40591,7 @@
       </c>
       <c r="AB366" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements, only alcohol ingestion.</t>
+          <t>Narrative discusses alcohol intoxication and does not mention any vitamin or fish oil.</t>
         </is>
       </c>
     </row>
@@ -40697,7 +40697,7 @@
       </c>
       <c r="AB367" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements, only household chemical (hair dye foam) and accidental ingestion.</t>
+          <t>Ingestion of 'hair dyefoamer' is a household chemical/toxin, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -40803,7 +40803,7 @@
       </c>
       <c r="AB368" t="inlineStr">
         <is>
-          <t>Mentions 'POISONING' which implies ingestion of a toxic substance (windshield fluid) rather than a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -40909,7 +40909,7 @@
       </c>
       <c r="AB369" t="inlineStr">
         <is>
-          <t>Glyburide is an OTC medication, not a supplement.</t>
+          <t>Mentions 'Glyburide tablets', which is a medication, excluded.</t>
         </is>
       </c>
     </row>
@@ -41027,7 +41027,7 @@
       </c>
       <c r="AB370" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements, only a new body wash.</t>
+          <t>The narrative describes using a 'body wash' which is a household product, not a vitamin or specified supplement.</t>
         </is>
       </c>
     </row>
@@ -41133,7 +41133,7 @@
       </c>
       <c r="AB371" t="inlineStr">
         <is>
-          <t>Mentions '***icillin' which is an antibiotic medication, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -41239,7 +41239,7 @@
       </c>
       <c r="AB372" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements; only mentions alcohol intoxication.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -41357,7 +41357,7 @@
       </c>
       <c r="AB373" t="inlineStr">
         <is>
-          <t>Tecfidera is a medication, not a supplement.</t>
+          <t>Mentions 'TECFIDERA', which is a medication, excluded.</t>
         </is>
       </c>
     </row>
@@ -41463,7 +41463,7 @@
       </c>
       <c r="AB374" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements; seizure caused by ethanol ingestion.</t>
+          <t>Narrative describes alcohol ingestion and seizure, with no mention of a vitamin or fish oil.</t>
         </is>
       </c>
     </row>
@@ -41569,7 +41569,7 @@
       </c>
       <c r="AB375" t="inlineStr">
         <is>
-          <t>Mentions 'drug overdose' and 'pill', which implies prescription medication, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -41674,7 +41674,7 @@
       </c>
       <c r="AB376" t="inlineStr">
         <is>
-          <t>No explicit mention of vitamin or dietary supplement, and mentions 'accidental drug ingestion' which implies a prescription medication.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -41780,7 +41780,7 @@
       </c>
       <c r="AB377" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements.</t>
+          <t>Narrative describes trauma and alcohol intoxication, with no mention of vitamins or relevant supplements.</t>
         </is>
       </c>
     </row>
@@ -41898,7 +41898,7 @@
       </c>
       <c r="AB378" t="inlineStr">
         <is>
-          <t>Mentions 'METFORMIN' which is a prescription medication, not a supplement.</t>
+          <t>Mentions 'METFORMIN', which is a medication, excluded.</t>
         </is>
       </c>
     </row>
@@ -42004,7 +42004,7 @@
       </c>
       <c r="AB379" t="inlineStr">
         <is>
-          <t>Empty bottle and induced vomiting suggest accidental ingestion of medication, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -42110,7 +42110,7 @@
       </c>
       <c r="AB380" t="inlineStr">
         <is>
-          <t>Body glitter is a cosmetic or decorative item, not a dietary supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -42216,7 +42216,7 @@
       </c>
       <c r="AB381" t="inlineStr">
         <is>
-          <t>Nail polish remover is a household chemical, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -42322,7 +42322,7 @@
       </c>
       <c r="AB382" t="inlineStr">
         <is>
-          <t>Mentions 'cleaning products' which are household chemicals, not supplements.</t>
+          <t>Narrative mentions 'cleaning products' which are household chemicals/toxins, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -42428,7 +42428,7 @@
       </c>
       <c r="AB383" t="inlineStr">
         <is>
-          <t>Cough medicine is medication, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -42534,7 +42534,7 @@
       </c>
       <c r="AB384" t="inlineStr">
         <is>
-          <t>Ingestion alone does NOT imply label=1; no specific vitamin/supplement mentioned.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -42652,7 +42652,7 @@
       </c>
       <c r="AB385" t="inlineStr">
         <is>
-          <t>Mentions '*** tablets' which are likely medication (amphetamine) and not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -42762,7 +42762,7 @@
       </c>
       <c r="AB386" t="inlineStr">
         <is>
-          <t>Mentions iron formulation (e.g., 'iron/Fe/ferrous'); iron-containing products are excluded.</t>
+          <t>Hard Rule: Mentions iron formulation.</t>
         </is>
       </c>
     </row>
@@ -42868,7 +42868,7 @@
       </c>
       <c r="AB387" t="inlineStr">
         <is>
-          <t>Cough syrup is medication, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -42974,7 +42974,7 @@
       </c>
       <c r="AB388" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -43080,7 +43080,7 @@
       </c>
       <c r="AB389" t="inlineStr">
         <is>
-          <t>Hypoglycemia medication is not a vitamin or dietary supplement, and the narrative does not mention any vitamin/supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -43186,7 +43186,7 @@
       </c>
       <c r="AB390" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements; no explicit ingestion of iron-containing formulation.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -43292,7 +43292,7 @@
       </c>
       <c r="AB391" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements; narrative is about police chase and injury from fall.</t>
+          <t>Narrative describes trauma/intoxication (EtOH) and does not mention any vitamin or fish oil.</t>
         </is>
       </c>
     </row>
@@ -43410,7 +43410,7 @@
       </c>
       <c r="AB392" t="inlineStr">
         <is>
-          <t>Mentions 'METOPROLOL' which is a medication, not a supplement.</t>
+          <t>Mentions 'METROPOLOL', which is a medication, excluded.</t>
         </is>
       </c>
     </row>
@@ -43516,7 +43516,7 @@
       </c>
       <c r="AB393" t="inlineStr">
         <is>
-          <t>No explicit mention of vitamin or dietary supplement; 'non-toxic ingestion' does not imply a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -43622,7 +43622,7 @@
       </c>
       <c r="AB394" t="inlineStr">
         <is>
-          <t>Mentions 'sister's med' which implies prescription medication, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -43728,7 +43728,7 @@
       </c>
       <c r="AB395" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements, and the narrative does not clearly involve a vitamin or dietary supplement.</t>
+          <t>Narrative describes alcohol use and seizure activity, with no mention of a strictly harmless vitamin or fish oil.</t>
         </is>
       </c>
     </row>
@@ -43834,7 +43834,7 @@
       </c>
       <c r="AB396" t="inlineStr">
         <is>
-          <t>Mentions '*** pills' without specifying a supplement or medication, so defaulting to label=0.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -43952,7 +43952,7 @@
       </c>
       <c r="AB397" t="inlineStr">
         <is>
-          <t>Mentions 'known medication' and specific name 'metformin', which is not a supplement.</t>
+          <t>Mentions 'METFORMIN', which is a prescription medication, excluded.</t>
         </is>
       </c>
     </row>
@@ -44070,7 +44070,7 @@
       </c>
       <c r="AB398" t="inlineStr">
         <is>
-          <t>No mention of vitamins or dietary supplements.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -44176,7 +44176,7 @@
       </c>
       <c r="AB399" t="inlineStr">
         <is>
-          <t>Caffeine is an OTC medication, not a supplement.</t>
+          <t>Mentions 'caffeine pill', which is not a vitamin or fish oil, and is a non-vitamin supplement.</t>
         </is>
       </c>
     </row>
@@ -44294,7 +44294,7 @@
       </c>
       <c r="AB400" t="inlineStr">
         <is>
-          <t>Mentions 'pre-workout supplement' which is a type of dietary supplement without specifying iron content.</t>
+          <t>Mentions 'pre-workout supplement' which is a non-vitamin supplement, excluded.</t>
         </is>
       </c>
     </row>
@@ -44400,7 +44400,7 @@
       </c>
       <c r="AB401" t="inlineStr">
         <is>
-          <t>Mentions 'rat poison' which is a household chemical/toxin, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -44506,7 +44506,7 @@
       </c>
       <c r="AB402" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements; narrative mentions mowing yard and angioedema.</t>
+          <t>Narrative describes angioedema, which is an adverse reaction, but does not mention ingestion of any vitamin or fish oil.</t>
         </is>
       </c>
     </row>
@@ -44612,7 +44612,7 @@
       </c>
       <c r="AB403" t="inlineStr">
         <is>
-          <t>No explicit mention of vitamin or dietary supplement, and presence of 'possible medication overdose' suggests it's not a supplement.</t>
+          <t>Narrative mentions 'possible medication overdose' and 'soda', which are not specified as a pure vitamin or fish oil.</t>
         </is>
       </c>
     </row>
@@ -44718,7 +44718,7 @@
       </c>
       <c r="AB404" t="inlineStr">
         <is>
-          <t>Unknown substance and no mention of vitamin or dietary supplement</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -44824,7 +44824,7 @@
       </c>
       <c r="AB405" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements; ingestion is accidental but no specific substance mentioned.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -44930,7 +44930,7 @@
       </c>
       <c r="AB406" t="inlineStr">
         <is>
-          <t>No explicit mention of vitamin or dietary supplement; ingestion alone does not imply label=1.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -45036,7 +45036,7 @@
       </c>
       <c r="AB407" t="inlineStr">
         <is>
-          <t>Mentions 'Clonezepam' which is an OTC medication, not a supplement.</t>
+          <t>Mentions 'CLONEZEPAM' which is a medication, excluded.</t>
         </is>
       </c>
     </row>
@@ -45158,7 +45158,7 @@
       </c>
       <c r="AB408" t="inlineStr">
         <is>
-          <t>Lisinopril and omeprazole are medications, not supplements.</t>
+          <t>Mentions 'lisinopril' and 'omeprazole' which are medications, excluded.</t>
         </is>
       </c>
     </row>
@@ -45264,7 +45264,7 @@
       </c>
       <c r="AB409" t="inlineStr">
         <is>
-          <t>Ingestion alone does NOT imply label=1 and 'unknown number' tablets do not specify a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -45374,7 +45374,7 @@
       </c>
       <c r="AB410" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements; ingestion is too vague.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -45496,7 +45496,7 @@
       </c>
       <c r="AB411" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements, only household chemicals (bleach) and symptoms.</t>
+          <t>Narrative describes chemical exposure (bleach) and does not involve any vitamin or fish oil ingestion.</t>
         </is>
       </c>
     </row>
@@ -45614,7 +45614,7 @@
       </c>
       <c r="AB412" t="inlineStr">
         <is>
-          <t>No explicit mention of vitamin or supplement ingestion, and no iron-containing formulation mentioned.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -45720,7 +45720,7 @@
       </c>
       <c r="AB413" t="inlineStr">
         <is>
-          <t>Mentions 'muscle rub ointment' which is a household chemical/toxin, not a supplement.</t>
+          <t>Mentions 'muscle rub ointment' which is a topical product, not a vitamin, and is not explicitly a vitamin or fish oil.</t>
         </is>
       </c>
     </row>
@@ -45826,7 +45826,7 @@
       </c>
       <c r="AB414" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements; ingestion is accidental but substance not identified.</t>
+          <t>Mentions 'rubbing etoh' which is a household chemical/toxin, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -45932,7 +45932,7 @@
       </c>
       <c r="AB415" t="inlineStr">
         <is>
-          <t>Ammonia is a household chemical, not a supplement.</t>
+          <t>Ingestion of ammonia inhalant stick is a household chemical/toxin, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -46038,7 +46038,7 @@
       </c>
       <c r="AB416" t="inlineStr">
         <is>
-          <t>Bleach is a household chemical, not a supplement.</t>
+          <t>Mentions 'BLEACH', which is a household chemical/toxin, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -46144,7 +46144,7 @@
       </c>
       <c r="AB417" t="inlineStr">
         <is>
-          <t>Mentions 'liquid meds' which are medications, not supplements.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -46250,7 +46250,7 @@
       </c>
       <c r="AB418" t="inlineStr">
         <is>
-          <t>No explicit mention of vitamin or dietary supplement; ingestion/dx accident is too vague to imply a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -46380,7 +46380,7 @@
       </c>
       <c r="AB419" t="inlineStr">
         <is>
-          <t>No mention of vitamins or dietary supplements.</t>
+          <t>Narrative discusses 'speedball' and 'alcoholic intoxication', which are not vitamins or fish oil.</t>
         </is>
       </c>
     </row>
@@ -46486,7 +46486,7 @@
       </c>
       <c r="AB420" t="inlineStr">
         <is>
-          <t>Mentions 'medication overdose' which implies prescription or OTC medication, not a supplement.</t>
+          <t>Narrative mentions 'MEDICATION OVERDOSE' and 'MEDS', indicating unknown or general medications, which are excluded.</t>
         </is>
       </c>
     </row>
@@ -46592,7 +46592,7 @@
       </c>
       <c r="AB421" t="inlineStr">
         <is>
-          <t>Mentions 'vitamin' but does not specify type or exclude iron, so default to 0.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -46698,7 +46698,7 @@
       </c>
       <c r="AB422" t="inlineStr">
         <is>
-          <t>No explicit mention of a vitamin or supplement, and no iron-containing formulation mentioned.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -46808,7 +46808,7 @@
       </c>
       <c r="AB423" t="inlineStr">
         <is>
-          <t>Mentions 'pills' but no specific supplement/vitamin mentioned; assumes medication ingestion</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -46926,7 +46926,7 @@
       </c>
       <c r="AB424" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements; mentions prescription medication 'glipizide'.</t>
+          <t>Mentions 'GLIPIZIDE' which is a medication, excluded.</t>
         </is>
       </c>
     </row>
@@ -47032,7 +47032,7 @@
       </c>
       <c r="AB425" t="inlineStr">
         <is>
-          <t>Mentions 'antifreeze' which is a household chemical/toxin, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -47138,7 +47138,7 @@
       </c>
       <c r="AB426" t="inlineStr">
         <is>
-          <t>No explicit mention of vitamin or supplement, and ingestion is not clearly linked to a known supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -47244,7 +47244,7 @@
       </c>
       <c r="AB427" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements; only mentions 'etoh' (alcohol) and 'weakness'.</t>
+          <t>Narrative describes alcohol ingestion and syncope, with no mention of a vitamin or fish oil.</t>
         </is>
       </c>
     </row>
@@ -47350,7 +47350,7 @@
       </c>
       <c r="AB428" t="inlineStr">
         <is>
-          <t>Air freshener is a household chemical, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -47472,7 +47472,7 @@
       </c>
       <c r="AB429" t="inlineStr">
         <is>
-          <t>Mentions 'laundry detergent' which is a chemical, not a supplement.</t>
+          <t>Ingestion of a household chemical ('detergent pod') is not a vitamin or fish oil.</t>
         </is>
       </c>
     </row>
@@ -47578,7 +47578,7 @@
       </c>
       <c r="AB430" t="inlineStr">
         <is>
-          <t>No explicit mention of a vitamin or supplement, and 'drug' is a general term for medication.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -47696,7 +47696,7 @@
       </c>
       <c r="AB431" t="inlineStr">
         <is>
-          <t>No explicit mention of a vitamin or supplement, and 'ER' likely refers to an emergency medication, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -47802,7 +47802,7 @@
       </c>
       <c r="AB432" t="inlineStr">
         <is>
-          <t>No explicit mention of vitamin or supplement; ingestion is accidental and involves unknown meds.</t>
+          <t>Mentions 'UNKNOWN MEDS' and 'MEDS', which are ambiguous/medications and are excluded.</t>
         </is>
       </c>
     </row>
@@ -47908,7 +47908,7 @@
       </c>
       <c r="AB433" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -48014,7 +48014,7 @@
       </c>
       <c r="AB434" t="inlineStr">
         <is>
-          <t>Mentions 'TAB/MED' which implies prescription medication, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -48120,7 +48120,7 @@
       </c>
       <c r="AB435" t="inlineStr">
         <is>
-          <t>Mentions 'medication' and 'ADHD pills', which are not supplements.</t>
+          <t>Mentions 'MEDICINE' (ADHD PILLS), which are medications and are excluded.</t>
         </is>
       </c>
     </row>
@@ -48226,7 +48226,7 @@
       </c>
       <c r="AB436" t="inlineStr">
         <is>
-          <t>Mentions 'mouthwash' which is a household chemical/toxin, not a supplement.</t>
+          <t>Mentions 'mouthwash' which is a household chemical/non-vitamin substance.</t>
         </is>
       </c>
     </row>
@@ -48332,7 +48332,7 @@
       </c>
       <c r="AB437" t="inlineStr">
         <is>
-          <t>Mentions 'multivitamin' but also mentions 'beta blocker pill', which is a medication.</t>
+          <t>Contains 'beta blocker pill' (a medication) and 'multivitamin' which is mixed with other substances, but the presence of a medication and the general mix makes it ambiguous/complex, defaulting to exclusion.</t>
         </is>
       </c>
     </row>
@@ -48438,7 +48438,7 @@
       </c>
       <c r="AB438" t="inlineStr">
         <is>
-          <t>No explicit mention of vitamin or supplement; only mentions 'pills' without specifying type.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -48544,7 +48544,7 @@
       </c>
       <c r="AB439" t="inlineStr">
         <is>
-          <t>Mentions 'bleach' which is a household chemical, not a supplement.</t>
+          <t>Ingestion of household chemical 'bleach' is not a vitamin and is excluded.</t>
         </is>
       </c>
     </row>
@@ -48662,7 +48662,7 @@
       </c>
       <c r="AB440" t="inlineStr">
         <is>
-          <t>Hand sanitizer is a household chemical, not a supplement.</t>
+          <t>Ingestion of hand sanitizer/alcohol is a household chemical/toxin, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -48776,11 +48776,11 @@
         <v>1</v>
       </c>
       <c r="AA441" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB441" t="inlineStr">
         <is>
-          <t>Mentions 'melatonin' (supplement; no iron) and is explicitly labeled as accidental poisoning.</t>
+          <t>Hard Rule: Mentions melatonin (non-vitamin supplement).</t>
         </is>
       </c>
     </row>
@@ -48898,7 +48898,7 @@
       </c>
       <c r="AB442" t="inlineStr">
         <is>
-          <t>Toilet cleaning stamp indicates ingestion of a corrosive chemical, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -49004,7 +49004,7 @@
       </c>
       <c r="AB443" t="inlineStr">
         <is>
-          <t>No explicit mention of vitamin or dietary supplement, and ingestion is not clearly related to a known supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -49114,7 +49114,7 @@
       </c>
       <c r="AB444" t="inlineStr">
         <is>
-          <t>No explicit mention of a vitamin or supplement, and 'pills' could refer to medication.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -49220,7 +49220,7 @@
       </c>
       <c r="AB445" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements, and bleach is a household chemical.</t>
+          <t>Involves household chemical 'bleach', not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -49338,7 +49338,7 @@
       </c>
       <c r="AB446" t="inlineStr">
         <is>
-          <t>Mentions 'tablets' without specifying a supplement, and contains medication keywords ('IMMEDIATE RELEASE', 'DRUG INGESTION')</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -49444,7 +49444,7 @@
       </c>
       <c r="AB447" t="inlineStr">
         <is>
-          <t>Amitriptyline is an OTC medication, not a supplement.</t>
+          <t>Mentions 'Amitriptyline' which is a medication, excluded.</t>
         </is>
       </c>
     </row>
@@ -49550,7 +49550,7 @@
       </c>
       <c r="AB448" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements.</t>
+          <t>Narrative describes alcohol intoxication and does not mention any vitamin or fish oil ingestion.</t>
         </is>
       </c>
     </row>
@@ -49660,7 +49660,7 @@
       </c>
       <c r="AB449" t="inlineStr">
         <is>
-          <t>Mentions 'drug overdose' which implies medication, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -49770,7 +49770,7 @@
       </c>
       <c r="AB450" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements; mentions immunizations and fever treatment.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -49876,7 +49876,7 @@
       </c>
       <c r="AB451" t="inlineStr">
         <is>
-          <t>No explicit mention of a vitamin or supplement, and mentions 'drug od' which implies prescription medication ingestion.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -49982,7 +49982,7 @@
       </c>
       <c r="AB452" t="inlineStr">
         <is>
-          <t>IBUPROFEN is an OTC medication, not a supplement.</t>
+          <t>Mentions 'Ibuprofen', which is a medication, excluded.</t>
         </is>
       </c>
     </row>
@@ -50088,7 +50088,7 @@
       </c>
       <c r="AB453" t="inlineStr">
         <is>
-          <t>Bleach is a household chemical, not a supplement.</t>
+          <t>Mentions 'BLEACH', which is a household chemical/toxin, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -50194,7 +50194,7 @@
       </c>
       <c r="AB454" t="inlineStr">
         <is>
-          <t>No explicit mention of a vitamin or supplement; ingestion is accidental and substance unknown.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -50300,7 +50300,7 @@
       </c>
       <c r="AB455" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements; ingestion is to unknown substance.</t>
+          <t>Narrative describes 'DXETOH INTOXICATION' which is not a vitamin, fish oil, or explicitly safe vitamin.</t>
         </is>
       </c>
     </row>
@@ -50406,7 +50406,7 @@
       </c>
       <c r="AB456" t="inlineStr">
         <is>
-          <t>Mentions 'glyburide tablet' which is an OTC medication, not a supplement.</t>
+          <t>Mentions 'GLYBURIDE TABLET', which is a medication, excluded.</t>
         </is>
       </c>
     </row>
@@ -50532,7 +50532,7 @@
       </c>
       <c r="AB457" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements; mentions 'medication side effect' which implies prescription medication.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -50638,7 +50638,7 @@
       </c>
       <c r="AB458" t="inlineStr">
         <is>
-          <t>No explicit mention of vitamin or dietary supplement; ingestion is to an unspecified substance.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -50748,7 +50748,7 @@
       </c>
       <c r="AB459" t="inlineStr">
         <is>
-          <t>No explicit mention of vitamin or dietary supplement; cannot determine if ingestion was related to a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -50866,7 +50866,7 @@
       </c>
       <c r="AB460" t="inlineStr">
         <is>
-          <t>Blood pressure pill is medication, not a supplement.</t>
+          <t>Mentions 'blood pressure pill', which is a medication, excluded.</t>
         </is>
       </c>
     </row>
@@ -50996,7 +50996,7 @@
       </c>
       <c r="AB461" t="inlineStr">
         <is>
-          <t>No mention of vitamins or dietary supplements.</t>
+          <t>Mentions 'COCAINE' which is a drug, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -51102,7 +51102,7 @@
       </c>
       <c r="AB462" t="inlineStr">
         <is>
-          <t>Deodorant is a household chemical, not a supplement.</t>
+          <t>Mentions 'DEODORANT' which is a household chemical/toxin, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -51208,7 +51208,7 @@
       </c>
       <c r="AB463" t="inlineStr">
         <is>
-          <t>RUBBING ALCHOHOL is a household chemical/toxin, not a vitamin/supplement.</t>
+          <t>Mentions 'rubbing alcohol' which is a household chemical/toxin, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -51314,7 +51314,7 @@
       </c>
       <c r="AB464" t="inlineStr">
         <is>
-          <t>No mention of vitamin or dietary supplement ingestion/exposure</t>
+          <t>Narrative describes exposure to gas vapors, not a vitamin or vitamin supplement.</t>
         </is>
       </c>
     </row>
@@ -51420,7 +51420,7 @@
       </c>
       <c r="AB465" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -51546,7 +51546,7 @@
       </c>
       <c r="AB466" t="inlineStr">
         <is>
-          <t>Narrative does not mention a vitamin or dietary supplement.</t>
+          <t>Narrative mentions 'overdose' and 'med' but does not specify a vitamin, nor does it meet the criteria for a clear, safe vitamin ingestion.</t>
         </is>
       </c>
     </row>
@@ -51664,7 +51664,7 @@
       </c>
       <c r="AB467" t="inlineStr">
         <is>
-          <t>Mentions 'OPTHALMIC SOLUTION' which is a medication, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -51774,7 +51774,7 @@
       </c>
       <c r="AB468" t="inlineStr">
         <is>
-          <t>Mentions 'shampoo' which is a household chemical, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -51880,7 +51880,7 @@
       </c>
       <c r="AB469" t="inlineStr">
         <is>
-          <t>No explicit mention of vitamin or dietary supplement; cannot determine if ingestion was related to a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -51986,7 +51986,7 @@
       </c>
       <c r="AB470" t="inlineStr">
         <is>
-          <t>Hydrogen peroxide is a household chemical/toxin, not a supplement.</t>
+          <t>Mentions 'HYDROGEN PEROXIDE', which is a household chemical/toxin, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -52092,7 +52092,7 @@
       </c>
       <c r="AB471" t="inlineStr">
         <is>
-          <t>Missing substance information; cannot determine if it's a vitamin/supplement or not.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -52198,7 +52198,7 @@
       </c>
       <c r="AB472" t="inlineStr">
         <is>
-          <t>Mentions 'VALIUM' which is a prescription medication, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -52304,7 +52304,7 @@
       </c>
       <c r="AB473" t="inlineStr">
         <is>
-          <t>No explicit mention of vitamin or dietary supplement; ingestion alone does not imply label=1.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -52434,7 +52434,7 @@
       </c>
       <c r="AB474" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements.</t>
+          <t>Narrative describes alcohol ingestion and seizure workup, with no mention of a strictly harmless vitamin or fish oil.</t>
         </is>
       </c>
     </row>
@@ -52544,7 +52544,7 @@
       </c>
       <c r="AB475" t="inlineStr">
         <is>
-          <t>Mentions 'metformin' which is a prescription medication, not a supplement.</t>
+          <t>Mentions 'Metformin', which is a prescription medication, excluded.</t>
         </is>
       </c>
     </row>
@@ -52650,7 +52650,7 @@
       </c>
       <c r="AB476" t="inlineStr">
         <is>
-          <t>Mentions 'glipiizide' and 'losartan', which are prescription medications, not supplements.</t>
+          <t>Mentions 'Gliipizide and Losartan', which are medications, excluded.</t>
         </is>
       </c>
     </row>
@@ -52756,7 +52756,7 @@
       </c>
       <c r="AB477" t="inlineStr">
         <is>
-          <t>No explicit mention of vitamin or supplement; ingestion alone does not imply label=1.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -52862,7 +52862,7 @@
       </c>
       <c r="AB478" t="inlineStr">
         <is>
-          <t>No explicit mention of vitamin or dietary supplement, and ingestion is not clearly linked to a known supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -52968,7 +52968,7 @@
       </c>
       <c r="AB479" t="inlineStr">
         <is>
-          <t>Unknown substance ingested, does not explicitly mention vitamin or dietary supplement</t>
+          <t>Mentions 'UNKNOWN PILL', which is ambiguous and not a specified vitamin.</t>
         </is>
       </c>
     </row>
@@ -53074,7 +53074,7 @@
       </c>
       <c r="AB480" t="inlineStr">
         <is>
-          <t>No explicit mention of a vitamin or supplement, and '***' is blank in the narrative.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -53180,7 +53180,7 @@
       </c>
       <c r="AB481" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements, and no indication of iron-containing formulation.</t>
+          <t>Narrative describes fall and intoxication, no vitamin ingestion mentioned.</t>
         </is>
       </c>
     </row>
@@ -53286,7 +53286,7 @@
       </c>
       <c r="AB482" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements.</t>
+          <t>Narrative describes alcohol intoxication and injury, with no mention of vitamin ingestion.</t>
         </is>
       </c>
     </row>
@@ -53404,7 +53404,7 @@
       </c>
       <c r="AB483" t="inlineStr">
         <is>
-          <t>No explicit mention of a vitamin or supplement; substance was identified as 'liquid used to clean tables' (household chemical).</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -53522,7 +53522,7 @@
       </c>
       <c r="AB484" t="inlineStr">
         <is>
-          <t>No mention of vitamin or supplement, only medication ingestion.</t>
+          <t>Mentions 'SERTRALINE', which is a prescription medication, excluded.</t>
         </is>
       </c>
     </row>
@@ -53640,7 +53640,7 @@
       </c>
       <c r="AB485" t="inlineStr">
         <is>
-          <t>Mentions 'toxic substance' which is not a supplement, but rather a household chemical.</t>
+          <t>Ingestion of antifreeze is a household chemical/toxin, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -53746,7 +53746,7 @@
       </c>
       <c r="AB486" t="inlineStr">
         <is>
-          <t>No mention of vitamin or dietary supplement; overdose context implies ingestion but no specific substance mentioned.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -53852,7 +53852,7 @@
       </c>
       <c r="AB487" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements; ingestion of 'alcoholic beverage' is not a supplement.</t>
+          <t>Ingestion of alcoholic beverage, which is not a vitamin or fish oil.</t>
         </is>
       </c>
     </row>
@@ -53970,7 +53970,7 @@
       </c>
       <c r="AB488" t="inlineStr">
         <is>
-          <t>Clonidine is a prescription medication, not a supplement.</t>
+          <t>Mentions 'CLONIDINE TABLETS', which is a medication, excluded.</t>
         </is>
       </c>
     </row>
@@ -54076,7 +54076,7 @@
       </c>
       <c r="AB489" t="inlineStr">
         <is>
-          <t>Lisinopril is an OTC medication, not a supplement.</t>
+          <t>Mentions 'LISINOPRIL TAB', which is a medication, excluded.</t>
         </is>
       </c>
     </row>
@@ -54186,7 +54186,7 @@
       </c>
       <c r="AB490" t="inlineStr">
         <is>
-          <t>No mention of vitamins or dietary supplements.</t>
+          <t>Narrative describes exposure to paint and symptoms, with no mention of vitamin ingestion.</t>
         </is>
       </c>
     </row>
@@ -54304,7 +54304,7 @@
       </c>
       <c r="AB491" t="inlineStr">
         <is>
-          <t>Mentions 'clonidine' which is a prescription medication, not a supplement.</t>
+          <t>Mentions 'CLONIDINE', which is a prescription medication, excluded.</t>
         </is>
       </c>
     </row>
@@ -54410,7 +54410,7 @@
       </c>
       <c r="AB492" t="inlineStr">
         <is>
-          <t>Mentions 'medication reaction' which implies prescription medication, not a supplement.</t>
+          <t>Narrative mentions 'MEDICATION REACTION' but does not specify ingestion of a pure, non-iron vitamin or fish oil.</t>
         </is>
       </c>
     </row>
@@ -54516,7 +54516,7 @@
       </c>
       <c r="AB493" t="inlineStr">
         <is>
-          <t>No explicit mention of vitamin or dietary supplement; accidental overdose implies ingestion but no clear indication of supplement type.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -54626,7 +54626,7 @@
       </c>
       <c r="AB494" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements, only medication (Lisinopril) and a medical condition.</t>
+          <t>Mentions 'LISINOPRIL', which is a prescription medication, excluded.</t>
         </is>
       </c>
     </row>
@@ -54744,7 +54744,7 @@
       </c>
       <c r="AB495" t="inlineStr">
         <is>
-          <t>Rat poison is a household chemical/toxin, not a supplement.</t>
+          <t>Ingestion of 'rat poison' is a household toxin, not a vitamin.</t>
         </is>
       </c>
     </row>
@@ -54850,7 +54850,7 @@
       </c>
       <c r="AB496" t="inlineStr">
         <is>
-          <t>No explicit mention of a vitamin or supplement, and ingestion alone does not imply label=1.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -54956,7 +54956,7 @@
       </c>
       <c r="AB497" t="inlineStr">
         <is>
-          <t>No mention of vitamins or supplements.</t>
+          <t>Narrative describes alcohol intoxication and fall, with no mention of vitamins or relevant supplements.</t>
         </is>
       </c>
     </row>
@@ -55062,7 +55062,7 @@
       </c>
       <c r="AB498" t="inlineStr">
         <is>
-          <t>Albuterol is a medication, not a supplement.</t>
+          <t>Mentions 'ALBUTEROLNEBULIZER SOLUTION', which is a medication, excluded.</t>
         </is>
       </c>
     </row>
@@ -55168,7 +55168,7 @@
       </c>
       <c r="AB499" t="inlineStr">
         <is>
-          <t>Mentions 'pill' which is a medication, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -55286,7 +55286,7 @@
       </c>
       <c r="AB500" t="inlineStr">
         <is>
-          <t>Mentions 'Benzodiazepine' which is a medication, not a supplement.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
@@ -55404,7 +55404,7 @@
       </c>
       <c r="AB501" t="inlineStr">
         <is>
-          <t>No mention of vitamin or dietary supplement; overdose could be any substance, including household chemicals.</t>
+          <t>Hard Rule: Contains redacted/ambiguous substance (***).</t>
         </is>
       </c>
     </row>
